--- a/research/traditional_assets/database/data/latvia/latvia_household_products.xlsx
+++ b/research/traditional_assets/database/data/latvia/latvia_household_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08592807841313595</v>
+        <v>0.08579222225630967</v>
       </c>
       <c r="C2">
-        <v>41.9</v>
+        <v>41.52076271049341</v>
       </c>
       <c r="D2">
-        <v>31.1</v>
+        <v>31.13976271049341</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.419</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.419</v>
       </c>
       <c r="G2">
         <v>10.8</v>
@@ -1451,28 +1451,28 @@
         <v>5.71</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0210757</v>
       </c>
       <c r="N2">
-        <v>5.71</v>
+        <v>5.6889243</v>
       </c>
       <c r="O2">
-        <v>1.142</v>
+        <v>1.13778486</v>
       </c>
       <c r="P2">
-        <v>4.568</v>
+        <v>4.55113944</v>
       </c>
       <c r="Q2">
-        <v>5.518</v>
+        <v>5.50113944</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08592807841313595</v>
+        <v>0.08625234571344412</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.6820846634426501</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>270.9281305010035</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08579222225630967</v>
+        <v>0.08565636609948339</v>
       </c>
       <c r="C3">
-        <v>41.52076271049341</v>
+        <v>41.14162722788101</v>
       </c>
       <c r="D3">
-        <v>31.13976271049341</v>
+        <v>31.17962722788101</v>
       </c>
       <c r="E3">
-        <v>0.419</v>
+        <v>0.838</v>
       </c>
       <c r="F3">
-        <v>0.419</v>
+        <v>0.838</v>
       </c>
       <c r="G3">
         <v>10.8</v>
@@ -1533,28 +1533,28 @@
         <v>5.71</v>
       </c>
       <c r="M3">
-        <v>0.0210757</v>
+        <v>0.0421514</v>
       </c>
       <c r="N3">
-        <v>5.6889243</v>
+        <v>5.6678486</v>
       </c>
       <c r="O3">
-        <v>1.13778486</v>
+        <v>1.13356972</v>
       </c>
       <c r="P3">
-        <v>4.55113944</v>
+        <v>4.53427888</v>
       </c>
       <c r="Q3">
-        <v>5.50113944</v>
+        <v>5.484278880000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08625234571344412</v>
+        <v>0.08658323071375856</v>
       </c>
       <c r="T3">
-        <v>0.6820846634426501</v>
+        <v>0.6876638599044933</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>270.9281305010035</v>
+        <v>135.4640652505018</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08565636609948339</v>
+        <v>0.08552050994265713</v>
       </c>
       <c r="C4">
-        <v>41.14162722788101</v>
+        <v>40.76259394365761</v>
       </c>
       <c r="D4">
-        <v>31.17962722788101</v>
+        <v>31.2195939436576</v>
       </c>
       <c r="E4">
-        <v>0.838</v>
+        <v>1.257</v>
       </c>
       <c r="F4">
-        <v>0.838</v>
+        <v>1.257</v>
       </c>
       <c r="G4">
         <v>10.8</v>
@@ -1615,28 +1615,28 @@
         <v>5.71</v>
       </c>
       <c r="M4">
-        <v>0.0421514</v>
+        <v>0.06322709999999999</v>
       </c>
       <c r="N4">
-        <v>5.6678486</v>
+        <v>5.6467729</v>
       </c>
       <c r="O4">
-        <v>1.13356972</v>
+        <v>1.12935458</v>
       </c>
       <c r="P4">
-        <v>4.53427888</v>
+        <v>4.51741832</v>
       </c>
       <c r="Q4">
-        <v>5.484278880000001</v>
+        <v>5.46741832</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08658323071375856</v>
+        <v>0.08692093808521353</v>
       </c>
       <c r="T4">
-        <v>0.6876638599044933</v>
+        <v>0.6933580913449313</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>135.4640652505018</v>
+        <v>90.30937683366786</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08552050994265713</v>
+        <v>0.08538465378583086</v>
       </c>
       <c r="C5">
-        <v>40.76259394365761</v>
+        <v>40.38366325132786</v>
       </c>
       <c r="D5">
-        <v>31.2195939436576</v>
+        <v>31.25966325132786</v>
       </c>
       <c r="E5">
-        <v>1.257</v>
+        <v>1.676</v>
       </c>
       <c r="F5">
-        <v>1.257</v>
+        <v>1.676</v>
       </c>
       <c r="G5">
         <v>10.8</v>
@@ -1697,28 +1697,28 @@
         <v>5.71</v>
       </c>
       <c r="M5">
-        <v>0.06322709999999999</v>
+        <v>0.0843028</v>
       </c>
       <c r="N5">
-        <v>5.6467729</v>
+        <v>5.6256972</v>
       </c>
       <c r="O5">
-        <v>1.12935458</v>
+        <v>1.12513944</v>
       </c>
       <c r="P5">
-        <v>4.51741832</v>
+        <v>4.50055776</v>
       </c>
       <c r="Q5">
-        <v>5.46741832</v>
+        <v>5.450557760000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08692093808521353</v>
+        <v>0.08726568102690715</v>
       </c>
       <c r="T5">
-        <v>0.6933580913449313</v>
+        <v>0.6991709526070452</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>90.30937683366786</v>
+        <v>67.73203262525088</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08538465378583086</v>
+        <v>0.08524879762900457</v>
       </c>
       <c r="C6">
-        <v>40.38366325132786</v>
+        <v>40.00483554641926</v>
       </c>
       <c r="D6">
-        <v>31.25966325132786</v>
+        <v>31.29983554641925</v>
       </c>
       <c r="E6">
-        <v>1.676</v>
+        <v>2.095</v>
       </c>
       <c r="F6">
-        <v>1.676</v>
+        <v>2.095</v>
       </c>
       <c r="G6">
         <v>10.8</v>
@@ -1779,28 +1779,28 @@
         <v>5.71</v>
       </c>
       <c r="M6">
-        <v>0.0843028</v>
+        <v>0.1053785</v>
       </c>
       <c r="N6">
-        <v>5.6256972</v>
+        <v>5.6046215</v>
       </c>
       <c r="O6">
-        <v>1.12513944</v>
+        <v>1.1209243</v>
       </c>
       <c r="P6">
-        <v>4.50055776</v>
+        <v>4.4836972</v>
       </c>
       <c r="Q6">
-        <v>5.450557760000001</v>
+        <v>5.4336972</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08726568102690715</v>
+        <v>0.08761768171474166</v>
       </c>
       <c r="T6">
-        <v>0.6991709526070452</v>
+        <v>0.7051061898957296</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>67.73203262525088</v>
+        <v>54.18562610020071</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08524879762900457</v>
+        <v>0.08511294147217829</v>
       </c>
       <c r="C7">
-        <v>40.00483554641926</v>
+        <v>39.62611122649505</v>
       </c>
       <c r="D7">
-        <v>31.29983554641925</v>
+        <v>31.34011122649505</v>
       </c>
       <c r="E7">
-        <v>2.095</v>
+        <v>2.514</v>
       </c>
       <c r="F7">
-        <v>2.095</v>
+        <v>2.514</v>
       </c>
       <c r="G7">
         <v>10.8</v>
@@ -1861,28 +1861,28 @@
         <v>5.71</v>
       </c>
       <c r="M7">
-        <v>0.1053785</v>
+        <v>0.1264542</v>
       </c>
       <c r="N7">
-        <v>5.6046215</v>
+        <v>5.5835458</v>
       </c>
       <c r="O7">
-        <v>1.1209243</v>
+        <v>1.11670916</v>
       </c>
       <c r="P7">
-        <v>4.4836972</v>
+        <v>4.466836639999999</v>
       </c>
       <c r="Q7">
-        <v>5.4336972</v>
+        <v>5.41683664</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08761768171474166</v>
+        <v>0.08797717177891309</v>
       </c>
       <c r="T7">
-        <v>0.7051061898957296</v>
+        <v>0.7111677088288544</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>54.18562610020071</v>
+        <v>45.15468841683391</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08511294147217829</v>
+        <v>0.08497708531535203</v>
       </c>
       <c r="C8">
-        <v>39.62611122649505</v>
+        <v>39.24749069116747</v>
       </c>
       <c r="D8">
-        <v>31.34011122649505</v>
+        <v>31.38049069116747</v>
       </c>
       <c r="E8">
-        <v>2.514</v>
+        <v>2.932999999999999</v>
       </c>
       <c r="F8">
-        <v>2.514</v>
+        <v>2.932999999999999</v>
       </c>
       <c r="G8">
         <v>10.8</v>
@@ -1943,28 +1943,28 @@
         <v>5.71</v>
       </c>
       <c r="M8">
-        <v>0.1264542</v>
+        <v>0.1475299</v>
       </c>
       <c r="N8">
-        <v>5.5835458</v>
+        <v>5.5624701</v>
       </c>
       <c r="O8">
-        <v>1.11670916</v>
+        <v>1.11249402</v>
       </c>
       <c r="P8">
-        <v>4.466836639999999</v>
+        <v>4.44997608</v>
       </c>
       <c r="Q8">
-        <v>5.41683664</v>
+        <v>5.39997608</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08797717177891309</v>
+        <v>0.08834439281220649</v>
       </c>
       <c r="T8">
-        <v>0.7111677088288544</v>
+        <v>0.7173595830078527</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>45.15468841683392</v>
+        <v>38.70401864300051</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08497708531535203</v>
+        <v>0.08484122915852578</v>
       </c>
       <c r="C9">
-        <v>39.24749069116747</v>
+        <v>38.86897434211085</v>
       </c>
       <c r="D9">
-        <v>31.38049069116747</v>
+        <v>31.42097434211085</v>
       </c>
       <c r="E9">
-        <v>2.933</v>
+        <v>3.352</v>
       </c>
       <c r="F9">
-        <v>2.933</v>
+        <v>3.352</v>
       </c>
       <c r="G9">
         <v>10.8</v>
@@ -2025,28 +2025,28 @@
         <v>5.71</v>
       </c>
       <c r="M9">
-        <v>0.1475299</v>
+        <v>0.1686056</v>
       </c>
       <c r="N9">
-        <v>5.5624701</v>
+        <v>5.5413944</v>
       </c>
       <c r="O9">
-        <v>1.11249402</v>
+        <v>1.10827888</v>
       </c>
       <c r="P9">
-        <v>4.44997608</v>
+        <v>4.433115519999999</v>
       </c>
       <c r="Q9">
-        <v>5.39997608</v>
+        <v>5.38311552</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08834439281220649</v>
+        <v>0.08871959691144106</v>
       </c>
       <c r="T9">
-        <v>0.7173595830078527</v>
+        <v>0.7236860631472641</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>38.7040186430005</v>
+        <v>33.86601631262544</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08484122915852578</v>
+        <v>0.0847053730016995</v>
       </c>
       <c r="C10">
-        <v>38.86897434211085</v>
+        <v>38.490562583075</v>
       </c>
       <c r="D10">
-        <v>31.42097434211085</v>
+        <v>31.461562583075</v>
       </c>
       <c r="E10">
-        <v>3.352</v>
+        <v>3.771</v>
       </c>
       <c r="F10">
-        <v>3.352</v>
+        <v>3.771</v>
       </c>
       <c r="G10">
         <v>10.8</v>
@@ -2107,28 +2107,28 @@
         <v>5.71</v>
       </c>
       <c r="M10">
-        <v>0.1686056</v>
+        <v>0.1896813</v>
       </c>
       <c r="N10">
-        <v>5.5413944</v>
+        <v>5.5203187</v>
       </c>
       <c r="O10">
-        <v>1.10827888</v>
+        <v>1.10406374</v>
       </c>
       <c r="P10">
-        <v>4.433115519999999</v>
+        <v>4.41625496</v>
       </c>
       <c r="Q10">
-        <v>5.38311552</v>
+        <v>5.36625496</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08871959691144106</v>
+        <v>0.08910304725461483</v>
       </c>
       <c r="T10">
-        <v>0.7236860631472641</v>
+        <v>0.7301515868062229</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>33.86601631262544</v>
+        <v>30.10312561122261</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0847053730016995</v>
+        <v>0.08456951684487321</v>
       </c>
       <c r="C11">
-        <v>38.490562583075</v>
+        <v>38.11225581989863</v>
       </c>
       <c r="D11">
-        <v>31.461562583075</v>
+        <v>31.50225581989863</v>
       </c>
       <c r="E11">
-        <v>3.771</v>
+        <v>4.19</v>
       </c>
       <c r="F11">
-        <v>3.771</v>
+        <v>4.19</v>
       </c>
       <c r="G11">
         <v>10.8</v>
@@ -2189,28 +2189,28 @@
         <v>5.71</v>
       </c>
       <c r="M11">
-        <v>0.1896813</v>
+        <v>0.210757</v>
       </c>
       <c r="N11">
-        <v>5.5203187</v>
+        <v>5.499243</v>
       </c>
       <c r="O11">
-        <v>1.10406374</v>
+        <v>1.0998486</v>
       </c>
       <c r="P11">
-        <v>4.41625496</v>
+        <v>4.3993944</v>
       </c>
       <c r="Q11">
-        <v>5.36625496</v>
+        <v>5.3493944</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08910304725461483</v>
+        <v>0.08949501871652579</v>
       </c>
       <c r="T11">
-        <v>0.7301515868062229</v>
+        <v>0.7367607887687141</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.10312561122261</v>
+        <v>27.09281305010035</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08456951684487324</v>
+        <v>0.08443366068804695</v>
       </c>
       <c r="C12">
-        <v>38.11225581989862</v>
+        <v>37.73405446052282</v>
       </c>
       <c r="D12">
-        <v>31.50225581989862</v>
+        <v>31.54305446052282</v>
       </c>
       <c r="E12">
-        <v>4.19</v>
+        <v>4.609</v>
       </c>
       <c r="F12">
-        <v>4.19</v>
+        <v>4.609</v>
       </c>
       <c r="G12">
         <v>10.8</v>
@@ -2271,28 +2271,28 @@
         <v>5.71</v>
       </c>
       <c r="M12">
-        <v>0.210757</v>
+        <v>0.2318327</v>
       </c>
       <c r="N12">
-        <v>5.499243</v>
+        <v>5.4781673</v>
       </c>
       <c r="O12">
-        <v>1.0998486</v>
+        <v>1.09563346</v>
       </c>
       <c r="P12">
-        <v>4.3993944</v>
+        <v>4.38253384</v>
       </c>
       <c r="Q12">
-        <v>5.3493944</v>
+        <v>5.33253384</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08949501871652582</v>
+        <v>0.08989579852589545</v>
       </c>
       <c r="T12">
-        <v>0.7367607887687143</v>
+        <v>0.743518512123621</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.09281305010035</v>
+        <v>24.62983004554578</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08443366068804695</v>
+        <v>0.08429780453122068</v>
       </c>
       <c r="C13">
-        <v>37.73405446052282</v>
+        <v>37.35595891500473</v>
       </c>
       <c r="D13">
-        <v>31.54305446052282</v>
+        <v>31.58395891500473</v>
       </c>
       <c r="E13">
-        <v>4.609</v>
+        <v>5.028</v>
       </c>
       <c r="F13">
-        <v>4.609</v>
+        <v>5.028</v>
       </c>
       <c r="G13">
         <v>10.8</v>
@@ -2353,28 +2353,28 @@
         <v>5.71</v>
       </c>
       <c r="M13">
-        <v>0.2318327</v>
+        <v>0.2529084</v>
       </c>
       <c r="N13">
-        <v>5.4781673</v>
+        <v>5.4570916</v>
       </c>
       <c r="O13">
-        <v>1.09563346</v>
+        <v>1.09141832</v>
       </c>
       <c r="P13">
-        <v>4.38253384</v>
+        <v>4.36567328</v>
       </c>
       <c r="Q13">
-        <v>5.33253384</v>
+        <v>5.31567328</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08989579852589545</v>
+        <v>0.09030568696729624</v>
       </c>
       <c r="T13">
-        <v>0.743518512123621</v>
+        <v>0.7504298201002303</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.62983004554578</v>
+        <v>22.57734420841696</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08429780453122068</v>
+        <v>0.0841619483743944</v>
       </c>
       <c r="C14">
-        <v>37.35595891500473</v>
+        <v>36.97796959553129</v>
       </c>
       <c r="D14">
-        <v>31.58395891500473</v>
+        <v>31.62496959553129</v>
       </c>
       <c r="E14">
-        <v>5.028</v>
+        <v>5.447</v>
       </c>
       <c r="F14">
-        <v>5.028</v>
+        <v>5.447</v>
       </c>
       <c r="G14">
         <v>10.8</v>
@@ -2435,28 +2435,28 @@
         <v>5.71</v>
       </c>
       <c r="M14">
-        <v>0.2529084</v>
+        <v>0.2739841</v>
       </c>
       <c r="N14">
-        <v>5.4570916</v>
+        <v>5.4360159</v>
       </c>
       <c r="O14">
-        <v>1.09141832</v>
+        <v>1.08720318</v>
       </c>
       <c r="P14">
-        <v>4.36567328</v>
+        <v>4.34881272</v>
       </c>
       <c r="Q14">
-        <v>5.31567328</v>
+        <v>5.29881272</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09030568696729624</v>
+        <v>0.09072499813148782</v>
       </c>
       <c r="T14">
-        <v>0.7504298201002303</v>
+        <v>0.7575000087199799</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.57734420841696</v>
+        <v>20.84062542315412</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0841619483743944</v>
+        <v>0.08402609221756814</v>
       </c>
       <c r="C15">
-        <v>36.97796959553129</v>
+        <v>36.60008691643304</v>
       </c>
       <c r="D15">
-        <v>31.62496959553129</v>
+        <v>31.66608691643304</v>
       </c>
       <c r="E15">
-        <v>5.447</v>
+        <v>5.866000000000001</v>
       </c>
       <c r="F15">
-        <v>5.447</v>
+        <v>5.866000000000001</v>
       </c>
       <c r="G15">
         <v>10.8</v>
@@ -2517,28 +2517,28 @@
         <v>5.71</v>
       </c>
       <c r="M15">
-        <v>0.2739841</v>
+        <v>0.2950598</v>
       </c>
       <c r="N15">
-        <v>5.4360159</v>
+        <v>5.4149402</v>
       </c>
       <c r="O15">
-        <v>1.08720318</v>
+        <v>1.08298804</v>
       </c>
       <c r="P15">
-        <v>4.34881272</v>
+        <v>4.33195216</v>
       </c>
       <c r="Q15">
-        <v>5.29881272</v>
+        <v>5.28195216</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09072499813148782</v>
+        <v>0.09115406071810249</v>
       </c>
       <c r="T15">
-        <v>0.7575000087199799</v>
+        <v>0.7647346203308866</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.84062542315412</v>
+        <v>19.35200932150025</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08402609221756814</v>
+        <v>0.08389023606074185</v>
       </c>
       <c r="C16">
-        <v>36.60008691643304</v>
+        <v>36.22231129419812</v>
       </c>
       <c r="D16">
-        <v>31.66608691643304</v>
+        <v>31.70731129419812</v>
       </c>
       <c r="E16">
-        <v>5.866000000000001</v>
+        <v>6.285000000000001</v>
       </c>
       <c r="F16">
-        <v>5.866000000000001</v>
+        <v>6.285000000000001</v>
       </c>
       <c r="G16">
         <v>10.8</v>
@@ -2599,28 +2599,28 @@
         <v>5.71</v>
       </c>
       <c r="M16">
-        <v>0.2950598</v>
+        <v>0.3161355</v>
       </c>
       <c r="N16">
-        <v>5.4149402</v>
+        <v>5.3938645</v>
       </c>
       <c r="O16">
-        <v>1.08298804</v>
+        <v>1.0787729</v>
       </c>
       <c r="P16">
-        <v>4.33195216</v>
+        <v>4.315091600000001</v>
       </c>
       <c r="Q16">
-        <v>5.28195216</v>
+        <v>5.265091600000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09115406071810249</v>
+        <v>0.09159321889499042</v>
       </c>
       <c r="T16">
-        <v>0.7647346203308866</v>
+        <v>0.7721394580973439</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.35200932150025</v>
+        <v>18.06187536673357</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08389023606074185</v>
+        <v>0.08375437990391559</v>
       </c>
       <c r="C17">
-        <v>36.22231129419813</v>
+        <v>35.84464314748629</v>
       </c>
       <c r="D17">
-        <v>31.70731129419812</v>
+        <v>31.74864314748629</v>
       </c>
       <c r="E17">
-        <v>6.284999999999999</v>
+        <v>6.704</v>
       </c>
       <c r="F17">
-        <v>6.284999999999999</v>
+        <v>6.704</v>
       </c>
       <c r="G17">
         <v>10.8</v>
@@ -2681,28 +2681,28 @@
         <v>5.71</v>
       </c>
       <c r="M17">
-        <v>0.3161355</v>
+        <v>0.3372112</v>
       </c>
       <c r="N17">
-        <v>5.3938645</v>
+        <v>5.3727888</v>
       </c>
       <c r="O17">
-        <v>1.0787729</v>
+        <v>1.07455776</v>
       </c>
       <c r="P17">
-        <v>4.315091600000001</v>
+        <v>4.29823104</v>
       </c>
       <c r="Q17">
-        <v>5.265091600000001</v>
+        <v>5.24823104</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09159321889499042</v>
+        <v>0.09204283321894713</v>
       </c>
       <c r="T17">
-        <v>0.7721394580973439</v>
+        <v>0.7797206015249074</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.06187536673357</v>
+        <v>16.93300815631272</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08375437990391559</v>
+        <v>0.08361852374708932</v>
       </c>
       <c r="C18">
-        <v>35.84464314748629</v>
+        <v>35.46708289714316</v>
       </c>
       <c r="D18">
-        <v>31.74864314748629</v>
+        <v>31.79008289714316</v>
       </c>
       <c r="E18">
-        <v>6.704</v>
+        <v>7.123</v>
       </c>
       <c r="F18">
-        <v>6.704</v>
+        <v>7.123</v>
       </c>
       <c r="G18">
         <v>10.8</v>
@@ -2763,28 +2763,28 @@
         <v>5.71</v>
       </c>
       <c r="M18">
-        <v>0.3372112</v>
+        <v>0.3582869</v>
       </c>
       <c r="N18">
-        <v>5.3727888</v>
+        <v>5.3517131</v>
       </c>
       <c r="O18">
-        <v>1.07455776</v>
+        <v>1.07034262</v>
       </c>
       <c r="P18">
-        <v>4.29823104</v>
+        <v>4.28137048</v>
       </c>
       <c r="Q18">
-        <v>5.24823104</v>
+        <v>5.23137048</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09204283321894713</v>
+        <v>0.09250328162299919</v>
       </c>
       <c r="T18">
-        <v>0.7797206015249074</v>
+        <v>0.787484423107352</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.93300815631272</v>
+        <v>15.9369488530002</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08361852374708932</v>
+        <v>0.08348266759026306</v>
       </c>
       <c r="C19">
-        <v>35.46708289714316</v>
+        <v>35.08963096621438</v>
       </c>
       <c r="D19">
-        <v>31.79008289714316</v>
+        <v>31.83163096621438</v>
       </c>
       <c r="E19">
-        <v>7.123</v>
+        <v>7.542000000000001</v>
       </c>
       <c r="F19">
-        <v>7.123</v>
+        <v>7.542000000000001</v>
       </c>
       <c r="G19">
         <v>10.8</v>
@@ -2845,28 +2845,28 @@
         <v>5.71</v>
       </c>
       <c r="M19">
-        <v>0.3582869</v>
+        <v>0.3793626</v>
       </c>
       <c r="N19">
-        <v>5.3517131</v>
+        <v>5.3306374</v>
       </c>
       <c r="O19">
-        <v>1.07034262</v>
+        <v>1.06612748</v>
       </c>
       <c r="P19">
-        <v>4.28137048</v>
+        <v>4.26450992</v>
       </c>
       <c r="Q19">
-        <v>5.23137048</v>
+        <v>5.21450992</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09250328162299919</v>
+        <v>0.09297496047593055</v>
       </c>
       <c r="T19">
-        <v>0.787484423107352</v>
+        <v>0.7954376061918075</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.9369488530002</v>
+        <v>15.05156280561131</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08348266759026306</v>
+        <v>0.08334681143343679</v>
       </c>
       <c r="C20">
-        <v>35.08963096621438</v>
+        <v>34.71228777996015</v>
       </c>
       <c r="D20">
-        <v>31.83163096621438</v>
+        <v>31.87328777996014</v>
       </c>
       <c r="E20">
-        <v>7.542</v>
+        <v>7.960999999999999</v>
       </c>
       <c r="F20">
-        <v>7.542</v>
+        <v>7.960999999999999</v>
       </c>
       <c r="G20">
         <v>10.8</v>
@@ -2927,28 +2927,28 @@
         <v>5.71</v>
       </c>
       <c r="M20">
-        <v>0.3793626</v>
+        <v>0.4004383</v>
       </c>
       <c r="N20">
-        <v>5.3306374</v>
+        <v>5.3095617</v>
       </c>
       <c r="O20">
-        <v>1.06612748</v>
+        <v>1.06191234</v>
       </c>
       <c r="P20">
-        <v>4.26450992</v>
+        <v>4.24764936</v>
       </c>
       <c r="Q20">
-        <v>5.21450992</v>
+        <v>5.19764936</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09297496047593054</v>
+        <v>0.09345828572029233</v>
       </c>
       <c r="T20">
-        <v>0.7954376061918074</v>
+        <v>0.8035871641672371</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.05156280561131</v>
+        <v>14.2593752895265</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08334681143343679</v>
+        <v>0.0832109552766105</v>
       </c>
       <c r="C21">
-        <v>34.71228777996015</v>
+        <v>34.33505376586964</v>
       </c>
       <c r="D21">
-        <v>31.87328777996014</v>
+        <v>31.91505376586964</v>
       </c>
       <c r="E21">
-        <v>7.960999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F21">
-        <v>7.960999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G21">
         <v>10.8</v>
@@ -3009,28 +3009,28 @@
         <v>5.71</v>
       </c>
       <c r="M21">
-        <v>0.4004383</v>
+        <v>0.421514</v>
       </c>
       <c r="N21">
-        <v>5.3095617</v>
+        <v>5.288486</v>
       </c>
       <c r="O21">
-        <v>1.06191234</v>
+        <v>1.0576972</v>
       </c>
       <c r="P21">
-        <v>4.24764936</v>
+        <v>4.2307888</v>
       </c>
       <c r="Q21">
-        <v>5.19764936</v>
+        <v>5.1807888</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09345828572029233</v>
+        <v>0.09395369409576312</v>
       </c>
       <c r="T21">
-        <v>0.8035871641672371</v>
+        <v>0.8119404610920523</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.2593752895265</v>
+        <v>13.54640652505018</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0832109552766105</v>
+        <v>0.08307509911978422</v>
       </c>
       <c r="C22">
-        <v>34.33505376586964</v>
+        <v>33.95792935367566</v>
       </c>
       <c r="D22">
-        <v>31.91505376586964</v>
+        <v>31.95692935367566</v>
       </c>
       <c r="E22">
-        <v>8.380000000000001</v>
+        <v>8.799000000000001</v>
       </c>
       <c r="F22">
-        <v>8.380000000000001</v>
+        <v>8.799000000000001</v>
       </c>
       <c r="G22">
         <v>10.8</v>
@@ -3091,28 +3091,28 @@
         <v>5.71</v>
       </c>
       <c r="M22">
-        <v>0.421514</v>
+        <v>0.4425897</v>
       </c>
       <c r="N22">
-        <v>5.288486</v>
+        <v>5.2674103</v>
       </c>
       <c r="O22">
-        <v>1.0576972</v>
+        <v>1.05348206</v>
       </c>
       <c r="P22">
-        <v>4.2307888</v>
+        <v>4.21392824</v>
       </c>
       <c r="Q22">
-        <v>5.1807888</v>
+        <v>5.16392824</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09395369409576312</v>
+        <v>0.09446164445542307</v>
       </c>
       <c r="T22">
-        <v>0.8119404610920523</v>
+        <v>0.820505233888382</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.54640652505018</v>
+        <v>12.90133954766683</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08307509911978422</v>
+        <v>0.08320324296295797</v>
       </c>
       <c r="C23">
-        <v>33.95792935367566</v>
+        <v>33.49942803048557</v>
       </c>
       <c r="D23">
-        <v>31.95692935367566</v>
+        <v>31.91742803048558</v>
       </c>
       <c r="E23">
-        <v>8.798999999999999</v>
+        <v>9.218</v>
       </c>
       <c r="F23">
-        <v>8.798999999999999</v>
+        <v>9.218</v>
       </c>
       <c r="G23">
         <v>10.8</v>
@@ -3173,45 +3173,45 @@
         <v>5.71</v>
       </c>
       <c r="M23">
-        <v>0.4425897</v>
+        <v>0.4774924</v>
       </c>
       <c r="N23">
-        <v>5.2674103</v>
+        <v>5.2325076</v>
       </c>
       <c r="O23">
-        <v>1.05348206</v>
+        <v>1.04650152</v>
       </c>
       <c r="P23">
-        <v>4.21392824</v>
+        <v>4.18600608</v>
       </c>
       <c r="Q23">
-        <v>5.16392824</v>
+        <v>5.13600608</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09446164445542307</v>
+        <v>0.09498261918327944</v>
       </c>
       <c r="T23">
-        <v>0.820505233888382</v>
+        <v>0.829289616243592</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>12.90133954766683</v>
+        <v>11.95830551439143</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08320324296295797</v>
+        <v>0.08307938680613171</v>
       </c>
       <c r="C24">
-        <v>33.49942803048557</v>
+        <v>33.11860606048411</v>
       </c>
       <c r="D24">
-        <v>31.91742803048558</v>
+        <v>31.95560606048411</v>
       </c>
       <c r="E24">
-        <v>9.218</v>
+        <v>9.637</v>
       </c>
       <c r="F24">
-        <v>9.218</v>
+        <v>9.637</v>
       </c>
       <c r="G24">
         <v>10.8</v>
@@ -3255,28 +3255,28 @@
         <v>5.71</v>
       </c>
       <c r="M24">
-        <v>0.4774924</v>
+        <v>0.4991966</v>
       </c>
       <c r="N24">
-        <v>5.2325076</v>
+        <v>5.2108034</v>
       </c>
       <c r="O24">
-        <v>1.04650152</v>
+        <v>1.04216068</v>
       </c>
       <c r="P24">
-        <v>4.18600608</v>
+        <v>4.168642719999999</v>
       </c>
       <c r="Q24">
-        <v>5.13600608</v>
+        <v>5.11864272</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09498261918327944</v>
+        <v>0.09551712572224896</v>
       </c>
       <c r="T24">
-        <v>0.829289616243592</v>
+        <v>0.838302164374262</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.95830551439143</v>
+        <v>11.43837918767876</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08307938680613171</v>
+        <v>0.08295553064930543</v>
       </c>
       <c r="C25">
-        <v>33.11860606048411</v>
+        <v>32.73787553315928</v>
       </c>
       <c r="D25">
-        <v>31.95560606048411</v>
+        <v>31.99387553315928</v>
       </c>
       <c r="E25">
-        <v>9.637</v>
+        <v>10.056</v>
       </c>
       <c r="F25">
-        <v>9.637</v>
+        <v>10.056</v>
       </c>
       <c r="G25">
         <v>10.8</v>
@@ -3337,28 +3337,28 @@
         <v>5.71</v>
       </c>
       <c r="M25">
-        <v>0.4991966</v>
+        <v>0.5209008000000001</v>
       </c>
       <c r="N25">
-        <v>5.2108034</v>
+        <v>5.1890992</v>
       </c>
       <c r="O25">
-        <v>1.04216068</v>
+        <v>1.03781984</v>
       </c>
       <c r="P25">
-        <v>4.168642719999999</v>
+        <v>4.15127936</v>
       </c>
       <c r="Q25">
-        <v>5.11864272</v>
+        <v>5.10127936</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09551712572224896</v>
+        <v>0.09606569822277029</v>
       </c>
       <c r="T25">
-        <v>0.838302164374262</v>
+        <v>0.84755188482416</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.43837918767876</v>
+        <v>10.96178005485881</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08295553064930541</v>
+        <v>0.08283167449247913</v>
       </c>
       <c r="C26">
-        <v>32.73787553315928</v>
+        <v>32.35723677743542</v>
       </c>
       <c r="D26">
-        <v>31.99387553315928</v>
+        <v>32.03223677743543</v>
       </c>
       <c r="E26">
-        <v>10.056</v>
+        <v>10.475</v>
       </c>
       <c r="F26">
-        <v>10.056</v>
+        <v>10.475</v>
       </c>
       <c r="G26">
         <v>10.8</v>
@@ -3419,28 +3419,28 @@
         <v>5.71</v>
       </c>
       <c r="M26">
-        <v>0.5209007999999999</v>
+        <v>0.542605</v>
       </c>
       <c r="N26">
-        <v>5.1890992</v>
+        <v>5.167395</v>
       </c>
       <c r="O26">
-        <v>1.03781984</v>
+        <v>1.033479</v>
       </c>
       <c r="P26">
-        <v>4.15127936</v>
+        <v>4.133916</v>
       </c>
       <c r="Q26">
-        <v>5.10127936</v>
+        <v>5.083916</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09606569822277028</v>
+        <v>0.09662889932330553</v>
       </c>
       <c r="T26">
-        <v>0.8475518848241599</v>
+        <v>0.8570482644860552</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.96178005485882</v>
+        <v>10.52330885266446</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08283167449247913</v>
+        <v>0.08270781833565288</v>
       </c>
       <c r="C27">
-        <v>32.35723677743542</v>
+        <v>31.97669012381633</v>
       </c>
       <c r="D27">
-        <v>32.03223677743543</v>
+        <v>32.07069012381633</v>
       </c>
       <c r="E27">
-        <v>10.475</v>
+        <v>10.894</v>
       </c>
       <c r="F27">
-        <v>10.475</v>
+        <v>10.894</v>
       </c>
       <c r="G27">
         <v>10.8</v>
@@ -3501,28 +3501,28 @@
         <v>5.71</v>
       </c>
       <c r="M27">
-        <v>0.542605</v>
+        <v>0.5643092</v>
       </c>
       <c r="N27">
-        <v>5.167395</v>
+        <v>5.1456908</v>
       </c>
       <c r="O27">
-        <v>1.033479</v>
+        <v>1.02913816</v>
       </c>
       <c r="P27">
-        <v>4.133916</v>
+        <v>4.11655264</v>
       </c>
       <c r="Q27">
-        <v>5.083916</v>
+        <v>5.06655264</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09662889932330553</v>
+        <v>0.09720732207520659</v>
       </c>
       <c r="T27">
-        <v>0.8570482644860552</v>
+        <v>0.8668013030577316</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.52330885266446</v>
+        <v>10.11856620448506</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08270781833565288</v>
+        <v>0.0829511621788266</v>
       </c>
       <c r="C28">
-        <v>31.97669012381633</v>
+        <v>31.48222699074451</v>
       </c>
       <c r="D28">
-        <v>32.07069012381633</v>
+        <v>31.99522699074451</v>
       </c>
       <c r="E28">
-        <v>10.894</v>
+        <v>11.313</v>
       </c>
       <c r="F28">
-        <v>10.894</v>
+        <v>11.313</v>
       </c>
       <c r="G28">
         <v>10.8</v>
@@ -3583,45 +3583,45 @@
         <v>5.71</v>
       </c>
       <c r="M28">
-        <v>0.5643092</v>
+        <v>0.6052455</v>
       </c>
       <c r="N28">
-        <v>5.1456908</v>
+        <v>5.1047545</v>
       </c>
       <c r="O28">
-        <v>1.02913816</v>
+        <v>1.0209509</v>
       </c>
       <c r="P28">
-        <v>4.11655264</v>
+        <v>4.0838036</v>
       </c>
       <c r="Q28">
-        <v>5.06655264</v>
+        <v>5.033803600000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09720732207520659</v>
+        <v>0.09780159202578988</v>
       </c>
       <c r="T28">
-        <v>0.8668013030577316</v>
+        <v>0.8768215481656183</v>
       </c>
       <c r="U28">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>10.11856620448506</v>
+        <v>9.434188275666651</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0829511621788266</v>
+        <v>0.08284090602200034</v>
       </c>
       <c r="C29">
-        <v>31.48222699074451</v>
+        <v>31.09737437723869</v>
       </c>
       <c r="D29">
-        <v>31.99522699074451</v>
+        <v>32.02937437723869</v>
       </c>
       <c r="E29">
-        <v>11.313</v>
+        <v>11.732</v>
       </c>
       <c r="F29">
-        <v>11.313</v>
+        <v>11.732</v>
       </c>
       <c r="G29">
         <v>10.8</v>
@@ -3665,28 +3665,28 @@
         <v>5.71</v>
       </c>
       <c r="M29">
-        <v>0.6052455</v>
+        <v>0.6276620000000001</v>
       </c>
       <c r="N29">
-        <v>5.1047545</v>
+        <v>5.082338</v>
       </c>
       <c r="O29">
-        <v>1.0209509</v>
+        <v>1.0164676</v>
       </c>
       <c r="P29">
-        <v>4.0838036</v>
+        <v>4.0658704</v>
       </c>
       <c r="Q29">
-        <v>5.033803600000001</v>
+        <v>5.0158704</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09780159202578988</v>
+        <v>0.09841236947500046</v>
       </c>
       <c r="T29">
-        <v>0.8768215481656183</v>
+        <v>0.8871201334153905</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.434188275666651</v>
+        <v>9.097252980107127</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08284090602200034</v>
+        <v>0.08273064986517406</v>
       </c>
       <c r="C30">
-        <v>31.09737437723869</v>
+        <v>30.71259473022955</v>
       </c>
       <c r="D30">
-        <v>32.02937437723869</v>
+        <v>32.06359473022955</v>
       </c>
       <c r="E30">
-        <v>11.732</v>
+        <v>12.151</v>
       </c>
       <c r="F30">
-        <v>11.732</v>
+        <v>12.151</v>
       </c>
       <c r="G30">
         <v>10.8</v>
@@ -3747,28 +3747,28 @@
         <v>5.71</v>
       </c>
       <c r="M30">
-        <v>0.6276620000000001</v>
+        <v>0.6500785000000001</v>
       </c>
       <c r="N30">
-        <v>5.082338</v>
+        <v>5.0599215</v>
       </c>
       <c r="O30">
-        <v>1.0164676</v>
+        <v>1.0119843</v>
       </c>
       <c r="P30">
-        <v>4.0658704</v>
+        <v>4.0479372</v>
       </c>
       <c r="Q30">
-        <v>5.0158704</v>
+        <v>4.9979372</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09841236947500046</v>
+        <v>0.09904035192278036</v>
       </c>
       <c r="T30">
-        <v>0.8871201334153905</v>
+        <v>0.8977088196581142</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.097252980107127</v>
+        <v>8.783554601482741</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08273064986517406</v>
+        <v>0.0826203937083478</v>
       </c>
       <c r="C31">
-        <v>30.71259473022955</v>
+        <v>30.3278882838406</v>
       </c>
       <c r="D31">
-        <v>32.06359473022955</v>
+        <v>32.0978882838406</v>
       </c>
       <c r="E31">
-        <v>12.151</v>
+        <v>12.57</v>
       </c>
       <c r="F31">
-        <v>12.151</v>
+        <v>12.57</v>
       </c>
       <c r="G31">
         <v>10.8</v>
@@ -3829,28 +3829,28 @@
         <v>5.71</v>
       </c>
       <c r="M31">
-        <v>0.6500784999999999</v>
+        <v>0.672495</v>
       </c>
       <c r="N31">
-        <v>5.0599215</v>
+        <v>5.037505</v>
       </c>
       <c r="O31">
-        <v>1.0119843</v>
+        <v>1.007501</v>
       </c>
       <c r="P31">
-        <v>4.0479372</v>
+        <v>4.030004</v>
       </c>
       <c r="Q31">
-        <v>4.9979372</v>
+        <v>4.980004</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09904035192278036</v>
+        <v>0.09968627672621114</v>
       </c>
       <c r="T31">
-        <v>0.8977088196581142</v>
+        <v>0.9086000397934872</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.783554601482745</v>
+        <v>8.490769448099986</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0826203937083478</v>
+        <v>0.08251013755152151</v>
       </c>
       <c r="C32">
-        <v>30.3278882838406</v>
+        <v>29.94325527319806</v>
       </c>
       <c r="D32">
-        <v>32.0978882838406</v>
+        <v>32.13225527319806</v>
       </c>
       <c r="E32">
-        <v>12.57</v>
+        <v>12.989</v>
       </c>
       <c r="F32">
-        <v>12.57</v>
+        <v>12.989</v>
       </c>
       <c r="G32">
         <v>10.8</v>
@@ -3911,28 +3911,28 @@
         <v>5.71</v>
       </c>
       <c r="M32">
-        <v>0.672495</v>
+        <v>0.6949114999999999</v>
       </c>
       <c r="N32">
-        <v>5.037505</v>
+        <v>5.0150885</v>
       </c>
       <c r="O32">
-        <v>1.007501</v>
+        <v>1.0030177</v>
       </c>
       <c r="P32">
-        <v>4.030004</v>
+        <v>4.0120708</v>
       </c>
       <c r="Q32">
-        <v>4.980004</v>
+        <v>4.9620708</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09968627672621114</v>
+        <v>0.1003509239877123</v>
       </c>
       <c r="T32">
-        <v>0.9086000397934872</v>
+        <v>0.9198069474690158</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.490769448099986</v>
+        <v>8.216873659451601</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08251013755152151</v>
+        <v>0.08239988139469523</v>
       </c>
       <c r="C33">
-        <v>29.94325527319806</v>
+        <v>29.55869593443619</v>
       </c>
       <c r="D33">
-        <v>32.13225527319806</v>
+        <v>32.16669593443618</v>
       </c>
       <c r="E33">
-        <v>12.989</v>
+        <v>13.408</v>
       </c>
       <c r="F33">
-        <v>12.989</v>
+        <v>13.408</v>
       </c>
       <c r="G33">
         <v>10.8</v>
@@ -3993,28 +3993,28 @@
         <v>5.71</v>
       </c>
       <c r="M33">
-        <v>0.6949114999999999</v>
+        <v>0.717328</v>
       </c>
       <c r="N33">
-        <v>5.0150885</v>
+        <v>4.992672</v>
       </c>
       <c r="O33">
-        <v>1.0030177</v>
+        <v>0.9985344</v>
       </c>
       <c r="P33">
-        <v>4.0120708</v>
+        <v>3.9941376</v>
       </c>
       <c r="Q33">
-        <v>4.9620708</v>
+        <v>4.944137599999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1003509239877123</v>
+        <v>0.1010351196980812</v>
       </c>
       <c r="T33">
-        <v>0.9198069474690158</v>
+        <v>0.9313434700761777</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.216873659451601</v>
+        <v>7.960096357593737</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08239988139469523</v>
+        <v>0.08228962523786895</v>
       </c>
       <c r="C34">
-        <v>29.55869593443619</v>
+        <v>29.17421050470276</v>
       </c>
       <c r="D34">
-        <v>32.16669593443618</v>
+        <v>32.20121050470276</v>
       </c>
       <c r="E34">
-        <v>13.408</v>
+        <v>13.827</v>
       </c>
       <c r="F34">
-        <v>13.408</v>
+        <v>13.827</v>
       </c>
       <c r="G34">
         <v>10.8</v>
@@ -4075,28 +4075,28 @@
         <v>5.71</v>
       </c>
       <c r="M34">
-        <v>0.717328</v>
+        <v>0.7397445</v>
       </c>
       <c r="N34">
-        <v>4.992672</v>
+        <v>4.9702555</v>
       </c>
       <c r="O34">
-        <v>0.9985344</v>
+        <v>0.9940511000000001</v>
       </c>
       <c r="P34">
-        <v>3.9941376</v>
+        <v>3.9762044</v>
       </c>
       <c r="Q34">
-        <v>4.944137599999999</v>
+        <v>4.9262044</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1010351196980812</v>
+        <v>0.1017397391609985</v>
       </c>
       <c r="T34">
-        <v>0.9313434700761777</v>
+        <v>0.9432243664925086</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.960096357593737</v>
+        <v>7.718881316454532</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08228962523786895</v>
+        <v>0.0823969690810427</v>
       </c>
       <c r="C35">
-        <v>29.17421050470276</v>
+        <v>28.72160665326985</v>
       </c>
       <c r="D35">
-        <v>32.20121050470276</v>
+        <v>32.16760665326986</v>
       </c>
       <c r="E35">
-        <v>13.827</v>
+        <v>14.246</v>
       </c>
       <c r="F35">
-        <v>13.827</v>
+        <v>14.246</v>
       </c>
       <c r="G35">
         <v>10.8</v>
@@ -4157,45 +4157,45 @@
         <v>5.71</v>
       </c>
       <c r="M35">
-        <v>0.7397445</v>
+        <v>0.7735578000000001</v>
       </c>
       <c r="N35">
-        <v>4.9702555</v>
+        <v>4.9364422</v>
       </c>
       <c r="O35">
-        <v>0.9940511000000001</v>
+        <v>0.98728844</v>
       </c>
       <c r="P35">
-        <v>3.9762044</v>
+        <v>3.94915376</v>
       </c>
       <c r="Q35">
-        <v>4.9262044</v>
+        <v>4.899153760000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1017397391609985</v>
+        <v>0.1024657107288526</v>
       </c>
       <c r="T35">
-        <v>0.9432243664925086</v>
+        <v>0.9554652900729708</v>
       </c>
       <c r="U35">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>7.718881316454532</v>
+        <v>7.381478151988125</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0823969690810427</v>
+        <v>0.08229311292421643</v>
       </c>
       <c r="C36">
-        <v>28.72160665326985</v>
+        <v>28.33511758552859</v>
       </c>
       <c r="D36">
-        <v>32.16760665326986</v>
+        <v>32.20011758552858</v>
       </c>
       <c r="E36">
-        <v>14.246</v>
+        <v>14.665</v>
       </c>
       <c r="F36">
-        <v>14.246</v>
+        <v>14.665</v>
       </c>
       <c r="G36">
         <v>10.8</v>
@@ -4239,28 +4239,28 @@
         <v>5.71</v>
       </c>
       <c r="M36">
-        <v>0.7735578000000001</v>
+        <v>0.7963095000000001</v>
       </c>
       <c r="N36">
-        <v>4.9364422</v>
+        <v>4.9136905</v>
       </c>
       <c r="O36">
-        <v>0.98728844</v>
+        <v>0.9827380999999999</v>
       </c>
       <c r="P36">
-        <v>3.94915376</v>
+        <v>3.9309524</v>
       </c>
       <c r="Q36">
-        <v>4.899153760000001</v>
+        <v>4.8809524</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1024657107288526</v>
+        <v>0.1032140198834099</v>
       </c>
       <c r="T36">
-        <v>0.9554652900729708</v>
+        <v>0.9680828574559086</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.381478151988125</v>
+        <v>7.170578776217035</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08229311292421643</v>
+        <v>0.08218925676739017</v>
       </c>
       <c r="C37">
-        <v>28.33511758552859</v>
+        <v>27.9486943001161</v>
       </c>
       <c r="D37">
-        <v>32.20011758552858</v>
+        <v>32.23269430011611</v>
       </c>
       <c r="E37">
-        <v>14.665</v>
+        <v>15.084</v>
       </c>
       <c r="F37">
-        <v>14.665</v>
+        <v>15.084</v>
       </c>
       <c r="G37">
         <v>10.8</v>
@@ -4321,28 +4321,28 @@
         <v>5.71</v>
       </c>
       <c r="M37">
-        <v>0.7963095000000001</v>
+        <v>0.8190612</v>
       </c>
       <c r="N37">
-        <v>4.9136905</v>
+        <v>4.8909388</v>
       </c>
       <c r="O37">
-        <v>0.9827380999999999</v>
+        <v>0.97818776</v>
       </c>
       <c r="P37">
-        <v>3.9309524</v>
+        <v>3.91275104</v>
       </c>
       <c r="Q37">
-        <v>4.8809524</v>
+        <v>4.86275104</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1032140198834099</v>
+        <v>0.1039857136990471</v>
       </c>
       <c r="T37">
-        <v>0.9680828574559086</v>
+        <v>0.9810947238195634</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.170578776217035</v>
+        <v>6.971396032433229</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08218925676739015</v>
+        <v>0.08208540061056388</v>
       </c>
       <c r="C38">
-        <v>27.94869430011611</v>
+        <v>27.5623369968897</v>
       </c>
       <c r="D38">
-        <v>32.23269430011611</v>
+        <v>32.26533699688969</v>
       </c>
       <c r="E38">
-        <v>15.084</v>
+        <v>15.503</v>
       </c>
       <c r="F38">
-        <v>15.084</v>
+        <v>15.503</v>
       </c>
       <c r="G38">
         <v>10.8</v>
@@ -4403,28 +4403,28 @@
         <v>5.71</v>
       </c>
       <c r="M38">
-        <v>0.8190612</v>
+        <v>0.8418129</v>
       </c>
       <c r="N38">
-        <v>4.8909388</v>
+        <v>4.8681871</v>
       </c>
       <c r="O38">
-        <v>0.97818776</v>
+        <v>0.9736374200000001</v>
       </c>
       <c r="P38">
-        <v>3.91275104</v>
+        <v>3.89454968</v>
       </c>
       <c r="Q38">
-        <v>4.86275104</v>
+        <v>4.84454968</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1039857136990471</v>
+        <v>0.1047819057310538</v>
       </c>
       <c r="T38">
-        <v>0.9810947238195633</v>
+        <v>0.9945196653058738</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.971396032433229</v>
+        <v>6.782979923448548</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08208540061056388</v>
+        <v>0.08198154445373761</v>
       </c>
       <c r="C39">
-        <v>27.5623369968897</v>
+        <v>27.17604587651701</v>
       </c>
       <c r="D39">
-        <v>32.26533699688969</v>
+        <v>32.298045876517</v>
       </c>
       <c r="E39">
-        <v>15.503</v>
+        <v>15.922</v>
       </c>
       <c r="F39">
-        <v>15.503</v>
+        <v>15.922</v>
       </c>
       <c r="G39">
         <v>10.8</v>
@@ -4485,28 +4485,28 @@
         <v>5.71</v>
       </c>
       <c r="M39">
-        <v>0.8418129</v>
+        <v>0.8645645999999999</v>
       </c>
       <c r="N39">
-        <v>4.8681871</v>
+        <v>4.8454354</v>
       </c>
       <c r="O39">
-        <v>0.9736374200000001</v>
+        <v>0.9690870800000001</v>
       </c>
       <c r="P39">
-        <v>3.89454968</v>
+        <v>3.87634832</v>
       </c>
       <c r="Q39">
-        <v>4.84454968</v>
+        <v>4.826348320000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1047819057310538</v>
+        <v>0.1056037813769961</v>
       </c>
       <c r="T39">
-        <v>0.9945196653058738</v>
+        <v>1.008377669420775</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.782979923448548</v>
+        <v>6.60448045177885</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08198154445373761</v>
+        <v>0.08187768829691133</v>
       </c>
       <c r="C40">
-        <v>27.17604587651701</v>
+        <v>26.78982114048025</v>
       </c>
       <c r="D40">
-        <v>32.298045876517</v>
+        <v>32.33082114048025</v>
       </c>
       <c r="E40">
-        <v>15.922</v>
+        <v>16.341</v>
       </c>
       <c r="F40">
-        <v>15.922</v>
+        <v>16.341</v>
       </c>
       <c r="G40">
         <v>10.8</v>
@@ -4567,28 +4567,28 @@
         <v>5.71</v>
       </c>
       <c r="M40">
-        <v>0.8645645999999999</v>
+        <v>0.8873163000000001</v>
       </c>
       <c r="N40">
-        <v>4.8454354</v>
+        <v>4.8226837</v>
       </c>
       <c r="O40">
-        <v>0.9690870800000001</v>
+        <v>0.96453674</v>
       </c>
       <c r="P40">
-        <v>3.87634832</v>
+        <v>3.85814696</v>
       </c>
       <c r="Q40">
-        <v>4.826348320000001</v>
+        <v>4.80814696</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1056037813769961</v>
+        <v>0.1064526037654284</v>
       </c>
       <c r="T40">
-        <v>1.008377669420775</v>
+        <v>1.022690034326328</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.60448045177885</v>
+        <v>6.435134799169134</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08187768829691133</v>
+        <v>0.08177383214008507</v>
       </c>
       <c r="C41">
-        <v>26.78982114048025</v>
+        <v>26.4036629910803</v>
       </c>
       <c r="D41">
-        <v>32.33082114048025</v>
+        <v>32.3636629910803</v>
       </c>
       <c r="E41">
-        <v>16.341</v>
+        <v>16.76</v>
       </c>
       <c r="F41">
-        <v>16.341</v>
+        <v>16.76</v>
       </c>
       <c r="G41">
         <v>10.8</v>
@@ -4649,28 +4649,28 @@
         <v>5.71</v>
       </c>
       <c r="M41">
-        <v>0.8873163000000001</v>
+        <v>0.9100680000000001</v>
       </c>
       <c r="N41">
-        <v>4.8226837</v>
+        <v>4.799932</v>
       </c>
       <c r="O41">
-        <v>0.96453674</v>
+        <v>0.9599864</v>
       </c>
       <c r="P41">
-        <v>3.85814696</v>
+        <v>3.8399456</v>
       </c>
       <c r="Q41">
-        <v>4.80814696</v>
+        <v>4.7899456</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1064526037654284</v>
+        <v>0.1073297202334751</v>
       </c>
       <c r="T41">
-        <v>1.022690034326328</v>
+        <v>1.037479478062067</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.435134799169134</v>
+        <v>6.274256429189906</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08177383214008507</v>
+        <v>0.0816699759832588</v>
       </c>
       <c r="C42">
-        <v>26.4036629910803</v>
+        <v>26.01757163144084</v>
       </c>
       <c r="D42">
-        <v>32.3636629910803</v>
+        <v>32.39657163144085</v>
       </c>
       <c r="E42">
-        <v>16.76</v>
+        <v>17.179</v>
       </c>
       <c r="F42">
-        <v>16.76</v>
+        <v>17.179</v>
       </c>
       <c r="G42">
         <v>10.8</v>
@@ -4731,28 +4731,28 @@
         <v>5.71</v>
       </c>
       <c r="M42">
-        <v>0.9100680000000001</v>
+        <v>0.9328197000000001</v>
       </c>
       <c r="N42">
-        <v>4.799932</v>
+        <v>4.777180299999999</v>
       </c>
       <c r="O42">
-        <v>0.9599864</v>
+        <v>0.9554360599999999</v>
       </c>
       <c r="P42">
-        <v>3.8399456</v>
+        <v>3.82174424</v>
       </c>
       <c r="Q42">
-        <v>4.7899456</v>
+        <v>4.77174424</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1073297202334751</v>
+        <v>0.1082365694631505</v>
       </c>
       <c r="T42">
-        <v>1.037479478062067</v>
+        <v>1.052770258873593</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.274256429189906</v>
+        <v>6.121225784575517</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0816699759832588</v>
+        <v>0.08190211982643253</v>
       </c>
       <c r="C43">
-        <v>26.01757163144084</v>
+        <v>25.5251049767811</v>
       </c>
       <c r="D43">
-        <v>32.39657163144085</v>
+        <v>32.32310497678111</v>
       </c>
       <c r="E43">
-        <v>17.179</v>
+        <v>17.598</v>
       </c>
       <c r="F43">
-        <v>17.179</v>
+        <v>17.598</v>
       </c>
       <c r="G43">
         <v>10.8</v>
@@ -4813,45 +4813,45 @@
         <v>5.71</v>
       </c>
       <c r="M43">
-        <v>0.9328197000000001</v>
+        <v>0.9731694000000002</v>
       </c>
       <c r="N43">
-        <v>4.777180299999999</v>
+        <v>4.736830599999999</v>
       </c>
       <c r="O43">
-        <v>0.9554360599999999</v>
+        <v>0.9473661199999999</v>
       </c>
       <c r="P43">
-        <v>3.82174424</v>
+        <v>3.789464479999999</v>
       </c>
       <c r="Q43">
-        <v>4.77174424</v>
+        <v>4.73946448</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1082365694631505</v>
+        <v>0.1091746893559182</v>
       </c>
       <c r="T43">
-        <v>1.052770258873593</v>
+        <v>1.068588307988966</v>
       </c>
       <c r="U43">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>6.121225784575517</v>
+        <v>5.867426575475964</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08190211982643253</v>
+        <v>0.08180626366960628</v>
       </c>
       <c r="C44">
-        <v>25.52510497678111</v>
+        <v>25.13640018791694</v>
       </c>
       <c r="D44">
-        <v>32.32310497678111</v>
+        <v>32.35340018791694</v>
       </c>
       <c r="E44">
-        <v>17.598</v>
+        <v>18.017</v>
       </c>
       <c r="F44">
-        <v>17.598</v>
+        <v>18.017</v>
       </c>
       <c r="G44">
         <v>10.8</v>
@@ -4895,28 +4895,28 @@
         <v>5.71</v>
       </c>
       <c r="M44">
-        <v>0.9731694</v>
+        <v>0.9963401</v>
       </c>
       <c r="N44">
-        <v>4.7368306</v>
+        <v>4.7136599</v>
       </c>
       <c r="O44">
-        <v>0.9473661200000001</v>
+        <v>0.94273198</v>
       </c>
       <c r="P44">
-        <v>3.78946448</v>
+        <v>3.77092792</v>
       </c>
       <c r="Q44">
-        <v>4.739464480000001</v>
+        <v>4.720927919999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1091746893559181</v>
+        <v>0.1101457257361513</v>
       </c>
       <c r="T44">
-        <v>1.068588307988965</v>
+        <v>1.084961376371544</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.867426575475966</v>
+        <v>5.730974794650943</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08180626366960628</v>
+        <v>0.08171040751277998</v>
       </c>
       <c r="C45">
-        <v>25.13640018791694</v>
+        <v>24.74775224141643</v>
       </c>
       <c r="D45">
-        <v>32.35340018791694</v>
+        <v>32.38375224141642</v>
       </c>
       <c r="E45">
-        <v>18.017</v>
+        <v>18.436</v>
       </c>
       <c r="F45">
-        <v>18.017</v>
+        <v>18.436</v>
       </c>
       <c r="G45">
         <v>10.8</v>
@@ -4977,28 +4977,28 @@
         <v>5.71</v>
       </c>
       <c r="M45">
-        <v>0.9963401</v>
+        <v>1.0195108</v>
       </c>
       <c r="N45">
-        <v>4.7136599</v>
+        <v>4.6904892</v>
       </c>
       <c r="O45">
-        <v>0.94273198</v>
+        <v>0.9380978400000001</v>
       </c>
       <c r="P45">
-        <v>3.77092792</v>
+        <v>3.75239136</v>
       </c>
       <c r="Q45">
-        <v>4.720927919999999</v>
+        <v>4.70239136</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1101457257361513</v>
+        <v>0.1111514419871071</v>
       </c>
       <c r="T45">
-        <v>1.084961376371544</v>
+        <v>1.101919197196357</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.730974794650943</v>
+        <v>5.600725367499786</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08171040751277998</v>
+        <v>0.08161455135595372</v>
       </c>
       <c r="C46">
-        <v>24.74775224141643</v>
+        <v>24.35916129740822</v>
       </c>
       <c r="D46">
-        <v>32.38375224141642</v>
+        <v>32.41416129740822</v>
       </c>
       <c r="E46">
-        <v>18.436</v>
+        <v>18.855</v>
       </c>
       <c r="F46">
-        <v>18.436</v>
+        <v>18.855</v>
       </c>
       <c r="G46">
         <v>10.8</v>
@@ -5059,28 +5059,28 @@
         <v>5.71</v>
       </c>
       <c r="M46">
-        <v>1.0195108</v>
+        <v>1.0426815</v>
       </c>
       <c r="N46">
-        <v>4.6904892</v>
+        <v>4.6673185</v>
       </c>
       <c r="O46">
-        <v>0.9380978400000001</v>
+        <v>0.9334637000000001</v>
       </c>
       <c r="P46">
-        <v>3.75239136</v>
+        <v>3.7338548</v>
       </c>
       <c r="Q46">
-        <v>4.70239136</v>
+        <v>4.683854800000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1111514419871071</v>
+        <v>0.1121937297380977</v>
       </c>
       <c r="T46">
-        <v>1.101919197196357</v>
+        <v>1.119493666051163</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.600725367499786</v>
+        <v>5.476264803777568</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08161455135595372</v>
+        <v>0.08151869519912745</v>
       </c>
       <c r="C47">
-        <v>24.35916129740822</v>
+        <v>23.97062751662307</v>
       </c>
       <c r="D47">
-        <v>32.41416129740822</v>
+        <v>32.44462751662306</v>
       </c>
       <c r="E47">
-        <v>18.855</v>
+        <v>19.274</v>
       </c>
       <c r="F47">
-        <v>18.855</v>
+        <v>19.274</v>
       </c>
       <c r="G47">
         <v>10.8</v>
@@ -5141,28 +5141,28 @@
         <v>5.71</v>
       </c>
       <c r="M47">
-        <v>1.0426815</v>
+        <v>1.0658522</v>
       </c>
       <c r="N47">
-        <v>4.6673185</v>
+        <v>4.6441478</v>
       </c>
       <c r="O47">
-        <v>0.9334637000000001</v>
+        <v>0.9288295600000001</v>
       </c>
       <c r="P47">
-        <v>3.7338548</v>
+        <v>3.71531824</v>
       </c>
       <c r="Q47">
-        <v>4.683854800000001</v>
+        <v>4.66531824</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1121937297380977</v>
+        <v>0.1132746207391249</v>
       </c>
       <c r="T47">
-        <v>1.119493666051163</v>
+        <v>1.137719041159851</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.476264803777568</v>
+        <v>5.357215568912837</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08151869519912745</v>
+        <v>0.08142283904230117</v>
       </c>
       <c r="C48">
-        <v>23.97062751662307</v>
+        <v>23.58215106039652</v>
       </c>
       <c r="D48">
-        <v>32.44462751662306</v>
+        <v>32.47515106039652</v>
       </c>
       <c r="E48">
-        <v>19.274</v>
+        <v>19.693</v>
       </c>
       <c r="F48">
-        <v>19.274</v>
+        <v>19.693</v>
       </c>
       <c r="G48">
         <v>10.8</v>
@@ -5223,28 +5223,28 @@
         <v>5.71</v>
       </c>
       <c r="M48">
-        <v>1.0658522</v>
+        <v>1.0890229</v>
       </c>
       <c r="N48">
-        <v>4.6441478</v>
+        <v>4.6209771</v>
       </c>
       <c r="O48">
-        <v>0.9288295600000001</v>
+        <v>0.9241954200000001</v>
       </c>
       <c r="P48">
-        <v>3.71531824</v>
+        <v>3.69678168</v>
       </c>
       <c r="Q48">
-        <v>4.66531824</v>
+        <v>4.64678168</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1132746207391249</v>
+        <v>0.1143963000798135</v>
       </c>
       <c r="T48">
-        <v>1.137719041159851</v>
+        <v>1.156632166272641</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.357215568912837</v>
+        <v>5.243232258935969</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08142283904230117</v>
+        <v>0.08132698288547491</v>
       </c>
       <c r="C49">
-        <v>23.58215106039652</v>
+        <v>23.19373209067185</v>
       </c>
       <c r="D49">
-        <v>32.47515106039652</v>
+        <v>32.50573209067185</v>
       </c>
       <c r="E49">
-        <v>19.693</v>
+        <v>20.112</v>
       </c>
       <c r="F49">
-        <v>19.693</v>
+        <v>20.112</v>
       </c>
       <c r="G49">
         <v>10.8</v>
@@ -5305,28 +5305,28 @@
         <v>5.71</v>
       </c>
       <c r="M49">
-        <v>1.0890229</v>
+        <v>1.1121936</v>
       </c>
       <c r="N49">
-        <v>4.6209771</v>
+        <v>4.5978064</v>
       </c>
       <c r="O49">
-        <v>0.9241954200000001</v>
+        <v>0.9195612799999999</v>
       </c>
       <c r="P49">
-        <v>3.69678168</v>
+        <v>3.67824512</v>
       </c>
       <c r="Q49">
-        <v>4.64678168</v>
+        <v>4.62824512</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1143963000798135</v>
+        <v>0.1155611209336056</v>
       </c>
       <c r="T49">
-        <v>1.156632166272641</v>
+        <v>1.176272719274384</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.243232258935969</v>
+        <v>5.133998253541469</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08132698288547489</v>
+        <v>0.08123112672864863</v>
       </c>
       <c r="C50">
-        <v>23.19373209067185</v>
+        <v>22.8053707700029</v>
       </c>
       <c r="D50">
-        <v>32.50573209067186</v>
+        <v>32.5363707700029</v>
       </c>
       <c r="E50">
-        <v>20.112</v>
+        <v>20.531</v>
       </c>
       <c r="F50">
-        <v>20.112</v>
+        <v>20.531</v>
       </c>
       <c r="G50">
         <v>10.8</v>
@@ -5387,28 +5387,28 @@
         <v>5.71</v>
       </c>
       <c r="M50">
-        <v>1.1121936</v>
+        <v>1.1353643</v>
       </c>
       <c r="N50">
-        <v>4.5978064</v>
+        <v>4.5746357</v>
       </c>
       <c r="O50">
-        <v>0.9195612799999999</v>
+        <v>0.9149271400000001</v>
       </c>
       <c r="P50">
-        <v>3.67824512</v>
+        <v>3.65970856</v>
       </c>
       <c r="Q50">
-        <v>4.62824512</v>
+        <v>4.60970856</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1155611209336056</v>
+        <v>0.1167716210365659</v>
       </c>
       <c r="T50">
-        <v>1.176272719274384</v>
+        <v>1.196683490040901</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.13399825354147</v>
+        <v>5.029222778979399</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08123112672864863</v>
+        <v>0.08113527057182235</v>
       </c>
       <c r="C51">
-        <v>22.8053707700029</v>
+        <v>22.41706726155696</v>
       </c>
       <c r="D51">
-        <v>32.5363707700029</v>
+        <v>32.56706726155695</v>
       </c>
       <c r="E51">
-        <v>20.531</v>
+        <v>20.95</v>
       </c>
       <c r="F51">
-        <v>20.531</v>
+        <v>20.95</v>
       </c>
       <c r="G51">
         <v>10.8</v>
@@ -5469,28 +5469,28 @@
         <v>5.71</v>
       </c>
       <c r="M51">
-        <v>1.1353643</v>
+        <v>1.158535</v>
       </c>
       <c r="N51">
-        <v>4.5746357</v>
+        <v>4.551465</v>
       </c>
       <c r="O51">
-        <v>0.9149271400000001</v>
+        <v>0.9102930000000001</v>
       </c>
       <c r="P51">
-        <v>3.65970856</v>
+        <v>3.641172</v>
       </c>
       <c r="Q51">
-        <v>4.60970856</v>
+        <v>4.591172</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1167716210365659</v>
+        <v>0.1180305411436447</v>
       </c>
       <c r="T51">
-        <v>1.196683490040901</v>
+        <v>1.217910691638079</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.029222778979399</v>
+        <v>4.928638323399811</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08113527057182235</v>
+        <v>0.08103941441499608</v>
       </c>
       <c r="C52">
-        <v>22.41706726155696</v>
+        <v>22.02882172911762</v>
       </c>
       <c r="D52">
-        <v>32.56706726155695</v>
+        <v>32.59782172911763</v>
       </c>
       <c r="E52">
-        <v>20.95</v>
+        <v>21.369</v>
       </c>
       <c r="F52">
-        <v>20.95</v>
+        <v>21.369</v>
       </c>
       <c r="G52">
         <v>10.8</v>
@@ -5551,28 +5551,28 @@
         <v>5.71</v>
       </c>
       <c r="M52">
-        <v>1.158535</v>
+        <v>1.1817057</v>
       </c>
       <c r="N52">
-        <v>4.551465</v>
+        <v>4.5282943</v>
       </c>
       <c r="O52">
-        <v>0.9102930000000001</v>
+        <v>0.90565886</v>
       </c>
       <c r="P52">
-        <v>3.641172</v>
+        <v>3.62263544</v>
       </c>
       <c r="Q52">
-        <v>4.591172</v>
+        <v>4.57263544</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1180305411436447</v>
+        <v>0.11934084574489</v>
       </c>
       <c r="T52">
-        <v>1.217910691638079</v>
+        <v>1.240004309626978</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.928638323399811</v>
+        <v>4.831998356274324</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08103941441499608</v>
+        <v>0.08094355825816982</v>
       </c>
       <c r="C53">
-        <v>22.02882172911762</v>
+        <v>21.64063433708783</v>
       </c>
       <c r="D53">
-        <v>32.59782172911763</v>
+        <v>32.62863433708782</v>
       </c>
       <c r="E53">
-        <v>21.369</v>
+        <v>21.788</v>
       </c>
       <c r="F53">
-        <v>21.369</v>
+        <v>21.788</v>
       </c>
       <c r="G53">
         <v>10.8</v>
@@ -5633,28 +5633,28 @@
         <v>5.71</v>
       </c>
       <c r="M53">
-        <v>1.1817057</v>
+        <v>1.2048764</v>
       </c>
       <c r="N53">
-        <v>4.5282943</v>
+        <v>4.5051236</v>
       </c>
       <c r="O53">
-        <v>0.90565886</v>
+        <v>0.9010247200000001</v>
       </c>
       <c r="P53">
-        <v>3.62263544</v>
+        <v>3.60409888</v>
       </c>
       <c r="Q53">
-        <v>4.57263544</v>
+        <v>4.55409888</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.11934084574489</v>
+        <v>0.1207057463711871</v>
       </c>
       <c r="T53">
-        <v>1.240004309626978</v>
+        <v>1.263018495032082</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.831998356274324</v>
+        <v>4.739075310961356</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08094355825816982</v>
+        <v>0.08084770210134354</v>
       </c>
       <c r="C54">
-        <v>21.64063433708783</v>
+        <v>21.25250525049261</v>
       </c>
       <c r="D54">
-        <v>32.62863433708782</v>
+        <v>32.65950525049261</v>
       </c>
       <c r="E54">
-        <v>21.788</v>
+        <v>22.207</v>
       </c>
       <c r="F54">
-        <v>21.788</v>
+        <v>22.207</v>
       </c>
       <c r="G54">
         <v>10.8</v>
@@ -5715,28 +5715,28 @@
         <v>5.71</v>
       </c>
       <c r="M54">
-        <v>1.2048764</v>
+        <v>1.2280471</v>
       </c>
       <c r="N54">
-        <v>4.5051236</v>
+        <v>4.4819529</v>
       </c>
       <c r="O54">
-        <v>0.9010247200000001</v>
+        <v>0.8963905799999999</v>
       </c>
       <c r="P54">
-        <v>3.60409888</v>
+        <v>3.58556232</v>
       </c>
       <c r="Q54">
-        <v>4.55409888</v>
+        <v>4.53556232</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1207057463711871</v>
+        <v>0.122128727875199</v>
       </c>
       <c r="T54">
-        <v>1.263018495032082</v>
+        <v>1.2870120074757</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.739075310961356</v>
+        <v>4.649658795660198</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08084770210134354</v>
+        <v>0.08075184594451726</v>
       </c>
       <c r="C55">
-        <v>21.25250525049261</v>
+        <v>20.86443463498216</v>
       </c>
       <c r="D55">
-        <v>32.65950525049261</v>
+        <v>32.69043463498217</v>
       </c>
       <c r="E55">
-        <v>22.207</v>
+        <v>22.626</v>
       </c>
       <c r="F55">
-        <v>22.207</v>
+        <v>22.626</v>
       </c>
       <c r="G55">
         <v>10.8</v>
@@ -5797,28 +5797,28 @@
         <v>5.71</v>
       </c>
       <c r="M55">
-        <v>1.2280471</v>
+        <v>1.2512178</v>
       </c>
       <c r="N55">
-        <v>4.4819529</v>
+        <v>4.4587822</v>
       </c>
       <c r="O55">
-        <v>0.8963905799999999</v>
+        <v>0.89175644</v>
       </c>
       <c r="P55">
-        <v>3.58556232</v>
+        <v>3.56702576</v>
       </c>
       <c r="Q55">
-        <v>4.53556232</v>
+        <v>4.51702576</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.122128727875199</v>
+        <v>0.1236135781402549</v>
       </c>
       <c r="T55">
-        <v>1.2870120074757</v>
+        <v>1.31204871611252</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.649658795660198</v>
+        <v>4.563554003147972</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08075184594451726</v>
+        <v>0.081755989787691</v>
       </c>
       <c r="C56">
-        <v>20.86443463498216</v>
+        <v>20.12431189539582</v>
       </c>
       <c r="D56">
-        <v>32.69043463498217</v>
+        <v>32.36931189539582</v>
       </c>
       <c r="E56">
-        <v>22.626</v>
+        <v>23.045</v>
       </c>
       <c r="F56">
-        <v>22.626</v>
+        <v>23.045</v>
       </c>
       <c r="G56">
         <v>10.8</v>
@@ -5879,45 +5879,45 @@
         <v>5.71</v>
       </c>
       <c r="M56">
-        <v>1.2512178</v>
+        <v>1.332001</v>
       </c>
       <c r="N56">
-        <v>4.4587822</v>
+        <v>4.377999</v>
       </c>
       <c r="O56">
-        <v>0.89175644</v>
+        <v>0.8755998</v>
       </c>
       <c r="P56">
-        <v>3.56702576</v>
+        <v>3.5023992</v>
       </c>
       <c r="Q56">
-        <v>4.51702576</v>
+        <v>4.4523992</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1236135781402549</v>
+        <v>0.1251644217504244</v>
       </c>
       <c r="T56">
-        <v>1.31204871611252</v>
+        <v>1.33819816735542</v>
       </c>
       <c r="U56">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V56">
         <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>4.563554003147972</v>
+        <v>4.286783568480804</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.081755989787691</v>
+        <v>0.08168013363086472</v>
       </c>
       <c r="C57">
-        <v>20.12431189539582</v>
+        <v>19.72935005064341</v>
       </c>
       <c r="D57">
-        <v>32.36931189539582</v>
+        <v>32.39335005064341</v>
       </c>
       <c r="E57">
-        <v>23.045</v>
+        <v>23.464</v>
       </c>
       <c r="F57">
-        <v>23.045</v>
+        <v>23.464</v>
       </c>
       <c r="G57">
         <v>10.8</v>
@@ -5961,28 +5961,28 @@
         <v>5.71</v>
       </c>
       <c r="M57">
-        <v>1.332001</v>
+        <v>1.3562192</v>
       </c>
       <c r="N57">
-        <v>4.377999</v>
+        <v>4.3537808</v>
       </c>
       <c r="O57">
-        <v>0.8755998</v>
+        <v>0.87075616</v>
       </c>
       <c r="P57">
-        <v>3.5023992</v>
+        <v>3.48302464</v>
       </c>
       <c r="Q57">
-        <v>4.4523992</v>
+        <v>4.43302464</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1251644217504244</v>
+        <v>0.1267857582519653</v>
       </c>
       <c r="T57">
-        <v>1.33819816735542</v>
+        <v>1.365536230018452</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.286783568480804</v>
+        <v>4.21023386190079</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08168013363086472</v>
+        <v>0.08160427747403845</v>
       </c>
       <c r="C58">
-        <v>19.72935005064341</v>
+        <v>19.33442393493831</v>
       </c>
       <c r="D58">
-        <v>32.39335005064341</v>
+        <v>32.41742393493831</v>
       </c>
       <c r="E58">
-        <v>23.464</v>
+        <v>23.883</v>
       </c>
       <c r="F58">
-        <v>23.464</v>
+        <v>23.883</v>
       </c>
       <c r="G58">
         <v>10.8</v>
@@ -6043,28 +6043,28 @@
         <v>5.71</v>
       </c>
       <c r="M58">
-        <v>1.3562192</v>
+        <v>1.3804374</v>
       </c>
       <c r="N58">
-        <v>4.3537808</v>
+        <v>4.3295626</v>
       </c>
       <c r="O58">
-        <v>0.87075616</v>
+        <v>0.8659125200000001</v>
       </c>
       <c r="P58">
-        <v>3.48302464</v>
+        <v>3.46365008</v>
       </c>
       <c r="Q58">
-        <v>4.43302464</v>
+        <v>4.41365008</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1267857582519653</v>
+        <v>0.1284825057535778</v>
       </c>
       <c r="T58">
-        <v>1.365536230018452</v>
+        <v>1.394145830479765</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.21023386190079</v>
+        <v>4.136370109937618</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08160427747403845</v>
+        <v>0.08152842131721219</v>
       </c>
       <c r="C59">
-        <v>19.33442393493831</v>
+        <v>18.9395336279984</v>
       </c>
       <c r="D59">
-        <v>32.41742393493831</v>
+        <v>32.4415336279984</v>
       </c>
       <c r="E59">
-        <v>23.883</v>
+        <v>24.302</v>
       </c>
       <c r="F59">
-        <v>23.883</v>
+        <v>24.302</v>
       </c>
       <c r="G59">
         <v>10.8</v>
@@ -6125,28 +6125,28 @@
         <v>5.71</v>
       </c>
       <c r="M59">
-        <v>1.3804374</v>
+        <v>1.4046556</v>
       </c>
       <c r="N59">
-        <v>4.3295626</v>
+        <v>4.305344399999999</v>
       </c>
       <c r="O59">
-        <v>0.8659125200000001</v>
+        <v>0.8610688799999999</v>
       </c>
       <c r="P59">
-        <v>3.46365008</v>
+        <v>3.444275519999999</v>
       </c>
       <c r="Q59">
-        <v>4.41365008</v>
+        <v>4.394275519999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1284825057535778</v>
+        <v>0.1302600507552671</v>
       </c>
       <c r="T59">
-        <v>1.394145830479765</v>
+        <v>1.424117792867807</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.136370109937618</v>
+        <v>4.06505338390421</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08152842131721216</v>
+        <v>0.0831045651603859</v>
       </c>
       <c r="C60">
-        <v>18.93953362799841</v>
+        <v>18.02683756648806</v>
       </c>
       <c r="D60">
-        <v>32.44153362799841</v>
+        <v>31.94783756648806</v>
       </c>
       <c r="E60">
-        <v>24.302</v>
+        <v>24.721</v>
       </c>
       <c r="F60">
-        <v>24.302</v>
+        <v>24.721</v>
       </c>
       <c r="G60">
         <v>10.8</v>
@@ -6207,45 +6207,45 @@
         <v>5.71</v>
       </c>
       <c r="M60">
-        <v>1.4046556</v>
+        <v>1.5153973</v>
       </c>
       <c r="N60">
-        <v>4.3053444</v>
+        <v>4.1946027</v>
       </c>
       <c r="O60">
-        <v>0.86106888</v>
+        <v>0.83892054</v>
       </c>
       <c r="P60">
-        <v>3.44427552</v>
+        <v>3.35568216</v>
       </c>
       <c r="Q60">
-        <v>4.394275520000001</v>
+        <v>4.30568216</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1302600507552671</v>
+        <v>0.1321243052692339</v>
       </c>
       <c r="T60">
-        <v>1.424117792867806</v>
+        <v>1.455551802201606</v>
       </c>
       <c r="U60">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V60">
         <v>0.2</v>
       </c>
       <c r="W60">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>4.065053383904211</v>
+        <v>3.767988764398617</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0831045651603859</v>
+        <v>0.08305670900355963</v>
       </c>
       <c r="C61">
-        <v>18.02683756648806</v>
+        <v>17.62260627231429</v>
       </c>
       <c r="D61">
-        <v>31.94783756648806</v>
+        <v>31.96260627231429</v>
       </c>
       <c r="E61">
-        <v>24.721</v>
+        <v>25.14</v>
       </c>
       <c r="F61">
-        <v>24.721</v>
+        <v>25.14</v>
       </c>
       <c r="G61">
         <v>10.8</v>
@@ -6289,28 +6289,28 @@
         <v>5.71</v>
       </c>
       <c r="M61">
-        <v>1.5153973</v>
+        <v>1.541082</v>
       </c>
       <c r="N61">
-        <v>4.1946027</v>
+        <v>4.168918</v>
       </c>
       <c r="O61">
-        <v>0.83892054</v>
+        <v>0.8337836</v>
       </c>
       <c r="P61">
-        <v>3.35568216</v>
+        <v>3.3351344</v>
       </c>
       <c r="Q61">
-        <v>4.30568216</v>
+        <v>4.2851344</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1321243052692339</v>
+        <v>0.1340817725088991</v>
       </c>
       <c r="T61">
-        <v>1.455551802201606</v>
+        <v>1.488557512002096</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.767988764398617</v>
+        <v>3.70518895165864</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08305670900355963</v>
+        <v>0.08300885284673336</v>
       </c>
       <c r="C62">
-        <v>17.62260627231429</v>
+        <v>17.21838863888027</v>
       </c>
       <c r="D62">
-        <v>31.96260627231429</v>
+        <v>31.97738863888027</v>
       </c>
       <c r="E62">
-        <v>25.14</v>
+        <v>25.559</v>
       </c>
       <c r="F62">
-        <v>25.14</v>
+        <v>25.559</v>
       </c>
       <c r="G62">
         <v>10.8</v>
@@ -6371,28 +6371,28 @@
         <v>5.71</v>
       </c>
       <c r="M62">
-        <v>1.541082</v>
+        <v>1.5667667</v>
       </c>
       <c r="N62">
-        <v>4.168918</v>
+        <v>4.1432333</v>
       </c>
       <c r="O62">
-        <v>0.8337836</v>
+        <v>0.8286466600000001</v>
       </c>
       <c r="P62">
-        <v>3.3351344</v>
+        <v>3.31458664</v>
       </c>
       <c r="Q62">
-        <v>4.2851344</v>
+        <v>4.264586640000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1340817725088991</v>
+        <v>0.1361396226839317</v>
       </c>
       <c r="T62">
-        <v>1.488557512002096</v>
+        <v>1.523255822305175</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.70518895165864</v>
+        <v>3.644448149172433</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08300885284673336</v>
+        <v>0.08296099668990708</v>
       </c>
       <c r="C63">
-        <v>17.21838863888027</v>
+        <v>16.81418468514864</v>
       </c>
       <c r="D63">
-        <v>31.97738863888027</v>
+        <v>31.99218468514863</v>
       </c>
       <c r="E63">
-        <v>25.559</v>
+        <v>25.978</v>
       </c>
       <c r="F63">
-        <v>25.559</v>
+        <v>25.978</v>
       </c>
       <c r="G63">
         <v>10.8</v>
@@ -6453,28 +6453,28 @@
         <v>5.71</v>
       </c>
       <c r="M63">
-        <v>1.5667667</v>
+        <v>1.5924514</v>
       </c>
       <c r="N63">
-        <v>4.1432333</v>
+        <v>4.1175486</v>
       </c>
       <c r="O63">
-        <v>0.8286466600000001</v>
+        <v>0.8235097200000001</v>
       </c>
       <c r="P63">
-        <v>3.31458664</v>
+        <v>3.29403888</v>
       </c>
       <c r="Q63">
-        <v>4.264586640000001</v>
+        <v>4.24403888</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1361396226839317</v>
+        <v>0.1383057807629134</v>
       </c>
       <c r="T63">
-        <v>1.523255822305175</v>
+        <v>1.559780359466311</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.644448149172433</v>
+        <v>3.585666727411587</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08296099668990708</v>
+        <v>0.08291314053308081</v>
       </c>
       <c r="C64">
-        <v>16.81418468514864</v>
+        <v>16.4099944301171</v>
       </c>
       <c r="D64">
-        <v>31.99218468514863</v>
+        <v>32.0069944301171</v>
       </c>
       <c r="E64">
-        <v>25.978</v>
+        <v>26.397</v>
       </c>
       <c r="F64">
-        <v>25.978</v>
+        <v>26.397</v>
       </c>
       <c r="G64">
         <v>10.8</v>
@@ -6535,28 +6535,28 @@
         <v>5.71</v>
       </c>
       <c r="M64">
-        <v>1.5924514</v>
+        <v>1.6181361</v>
       </c>
       <c r="N64">
-        <v>4.1175486</v>
+        <v>4.0918639</v>
       </c>
       <c r="O64">
-        <v>0.8235097200000001</v>
+        <v>0.81837278</v>
       </c>
       <c r="P64">
-        <v>3.29403888</v>
+        <v>3.27349112</v>
       </c>
       <c r="Q64">
-        <v>4.24403888</v>
+        <v>4.22349112</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1383057807629134</v>
+        <v>0.140589028467786</v>
       </c>
       <c r="T64">
-        <v>1.559780359466311</v>
+        <v>1.598279195933455</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.585666727411587</v>
+        <v>3.528751382532038</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08291314053308081</v>
+        <v>0.08429888437625455</v>
       </c>
       <c r="C65">
-        <v>16.4099944301171</v>
+        <v>15.56763336998228</v>
       </c>
       <c r="D65">
-        <v>32.0069944301171</v>
+        <v>31.58363336998228</v>
       </c>
       <c r="E65">
-        <v>26.397</v>
+        <v>26.816</v>
       </c>
       <c r="F65">
-        <v>26.397</v>
+        <v>26.816</v>
       </c>
       <c r="G65">
         <v>10.8</v>
@@ -6617,45 +6617,45 @@
         <v>5.71</v>
       </c>
       <c r="M65">
-        <v>1.6181361</v>
+        <v>1.7189056</v>
       </c>
       <c r="N65">
-        <v>4.0918639</v>
+        <v>3.9910944</v>
       </c>
       <c r="O65">
-        <v>0.81837278</v>
+        <v>0.79821888</v>
       </c>
       <c r="P65">
-        <v>3.27349112</v>
+        <v>3.19287552</v>
       </c>
       <c r="Q65">
-        <v>4.22349112</v>
+        <v>4.14287552</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.140589028467786</v>
+        <v>0.1429991232673737</v>
       </c>
       <c r="T65">
-        <v>1.598279195933455</v>
+        <v>1.638916856648773</v>
       </c>
       <c r="U65">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V65">
         <v>0.2</v>
       </c>
       <c r="W65">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.528751382532038</v>
+        <v>3.321881085267277</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08429888437625455</v>
+        <v>0.08427342821942826</v>
       </c>
       <c r="C66">
-        <v>15.56763336998228</v>
+        <v>15.15630952125132</v>
       </c>
       <c r="D66">
-        <v>31.58363336998228</v>
+        <v>31.59130952125132</v>
       </c>
       <c r="E66">
-        <v>26.816</v>
+        <v>27.235</v>
       </c>
       <c r="F66">
-        <v>26.816</v>
+        <v>27.235</v>
       </c>
       <c r="G66">
         <v>10.8</v>
@@ -6699,28 +6699,28 @@
         <v>5.71</v>
       </c>
       <c r="M66">
-        <v>1.7189056</v>
+        <v>1.7457635</v>
       </c>
       <c r="N66">
-        <v>3.9910944</v>
+        <v>3.9642365</v>
       </c>
       <c r="O66">
-        <v>0.79821888</v>
+        <v>0.7928473</v>
       </c>
       <c r="P66">
-        <v>3.19287552</v>
+        <v>3.1713892</v>
       </c>
       <c r="Q66">
-        <v>4.14287552</v>
+        <v>4.1213892</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1429991232673737</v>
+        <v>0.145546937769795</v>
       </c>
       <c r="T66">
-        <v>1.638916856648773</v>
+        <v>1.681876669404966</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.321881085267277</v>
+        <v>3.270775222417011</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08427342821942826</v>
+        <v>0.08424797206260201</v>
       </c>
       <c r="C67">
-        <v>15.15630952125132</v>
+        <v>14.74498940468265</v>
       </c>
       <c r="D67">
-        <v>31.59130952125132</v>
+        <v>31.59898940468265</v>
       </c>
       <c r="E67">
-        <v>27.235</v>
+        <v>27.654</v>
       </c>
       <c r="F67">
-        <v>27.235</v>
+        <v>27.654</v>
       </c>
       <c r="G67">
         <v>10.8</v>
@@ -6781,28 +6781,28 @@
         <v>5.71</v>
       </c>
       <c r="M67">
-        <v>1.7457635</v>
+        <v>1.7726214</v>
       </c>
       <c r="N67">
-        <v>3.9642365</v>
+        <v>3.9373786</v>
       </c>
       <c r="O67">
-        <v>0.7928473</v>
+        <v>0.78747572</v>
       </c>
       <c r="P67">
-        <v>3.1713892</v>
+        <v>3.14990288</v>
       </c>
       <c r="Q67">
-        <v>4.1213892</v>
+        <v>4.09990288</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.145546937769795</v>
+        <v>0.1482446237135353</v>
       </c>
       <c r="T67">
-        <v>1.681876669404966</v>
+        <v>1.727363529970347</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.270775222417011</v>
+        <v>3.221218022077359</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08424797206260201</v>
+        <v>0.08422251590577573</v>
       </c>
       <c r="C68">
-        <v>14.74498940468265</v>
+        <v>14.33367302299882</v>
       </c>
       <c r="D68">
-        <v>31.59898940468265</v>
+        <v>31.60667302299881</v>
       </c>
       <c r="E68">
-        <v>27.654</v>
+        <v>28.073</v>
       </c>
       <c r="F68">
-        <v>27.654</v>
+        <v>28.073</v>
       </c>
       <c r="G68">
         <v>10.8</v>
@@ -6863,28 +6863,28 @@
         <v>5.71</v>
       </c>
       <c r="M68">
-        <v>1.7726214</v>
+        <v>1.7994793</v>
       </c>
       <c r="N68">
-        <v>3.9373786</v>
+        <v>3.9105207</v>
       </c>
       <c r="O68">
-        <v>0.78747572</v>
+        <v>0.7821041399999999</v>
       </c>
       <c r="P68">
-        <v>3.14990288</v>
+        <v>3.12841656</v>
       </c>
       <c r="Q68">
-        <v>4.09990288</v>
+        <v>4.07841656</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1482446237135353</v>
+        <v>0.151105805775078</v>
       </c>
       <c r="T68">
-        <v>1.727363529970347</v>
+        <v>1.775607169963933</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.221218022077359</v>
+        <v>3.173140141150832</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08422251590577573</v>
+        <v>0.08419705974894946</v>
       </c>
       <c r="C69">
-        <v>14.33367302299882</v>
+        <v>13.92236037892499</v>
       </c>
       <c r="D69">
-        <v>31.60667302299881</v>
+        <v>31.61436037892499</v>
       </c>
       <c r="E69">
-        <v>28.073</v>
+        <v>28.492</v>
       </c>
       <c r="F69">
-        <v>28.073</v>
+        <v>28.492</v>
       </c>
       <c r="G69">
         <v>10.8</v>
@@ -6945,28 +6945,28 @@
         <v>5.71</v>
       </c>
       <c r="M69">
-        <v>1.7994793</v>
+        <v>1.8263372</v>
       </c>
       <c r="N69">
-        <v>3.9105207</v>
+        <v>3.8836628</v>
       </c>
       <c r="O69">
-        <v>0.7821041399999999</v>
+        <v>0.77673256</v>
       </c>
       <c r="P69">
-        <v>3.12841656</v>
+        <v>3.10693024</v>
       </c>
       <c r="Q69">
-        <v>4.07841656</v>
+        <v>4.05693024</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.151105805775078</v>
+        <v>0.1541458117154671</v>
       </c>
       <c r="T69">
-        <v>1.775607169963933</v>
+        <v>1.826866037457118</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.173140141150832</v>
+        <v>3.126476315545672</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08419705974894946</v>
+        <v>0.0841716035921232</v>
       </c>
       <c r="C70">
-        <v>13.92236037892499</v>
+        <v>13.51105147518901</v>
       </c>
       <c r="D70">
-        <v>31.61436037892499</v>
+        <v>31.62205147518901</v>
       </c>
       <c r="E70">
-        <v>28.492</v>
+        <v>28.911</v>
       </c>
       <c r="F70">
-        <v>28.492</v>
+        <v>28.911</v>
       </c>
       <c r="G70">
         <v>10.8</v>
@@ -7027,28 +7027,28 @@
         <v>5.71</v>
       </c>
       <c r="M70">
-        <v>1.8263372</v>
+        <v>1.8531951</v>
       </c>
       <c r="N70">
-        <v>3.8836628</v>
+        <v>3.8568049</v>
       </c>
       <c r="O70">
-        <v>0.77673256</v>
+        <v>0.77136098</v>
       </c>
       <c r="P70">
-        <v>3.10693024</v>
+        <v>3.08544392</v>
       </c>
       <c r="Q70">
-        <v>4.05693024</v>
+        <v>4.035443920000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1541458117154671</v>
+        <v>0.1573819470713651</v>
       </c>
       <c r="T70">
-        <v>1.826866037457118</v>
+        <v>1.881431928659541</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.126476315545672</v>
+        <v>3.081165064595735</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0841716035921232</v>
+        <v>0.08414614743529691</v>
       </c>
       <c r="C71">
-        <v>13.51105147518901</v>
+        <v>13.09974631452139</v>
       </c>
       <c r="D71">
-        <v>31.62205147518901</v>
+        <v>31.62974631452139</v>
       </c>
       <c r="E71">
-        <v>28.911</v>
+        <v>29.33</v>
       </c>
       <c r="F71">
-        <v>28.911</v>
+        <v>29.33</v>
       </c>
       <c r="G71">
         <v>10.8</v>
@@ -7109,28 +7109,28 @@
         <v>5.71</v>
       </c>
       <c r="M71">
-        <v>1.8531951</v>
+        <v>1.880053</v>
       </c>
       <c r="N71">
-        <v>3.8568049</v>
+        <v>3.829947</v>
       </c>
       <c r="O71">
-        <v>0.77136098</v>
+        <v>0.7659894</v>
       </c>
       <c r="P71">
-        <v>3.08544392</v>
+        <v>3.0639576</v>
       </c>
       <c r="Q71">
-        <v>4.035443920000001</v>
+        <v>4.013957599999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1573819470713651</v>
+        <v>0.1608338247843231</v>
       </c>
       <c r="T71">
-        <v>1.881431928659541</v>
+        <v>1.939635545942126</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.081165064595735</v>
+        <v>3.037148420815796</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08414614743529691</v>
+        <v>0.08855109127847066</v>
       </c>
       <c r="C72">
-        <v>13.09974631452139</v>
+        <v>11.40271840640883</v>
       </c>
       <c r="D72">
-        <v>31.62974631452139</v>
+        <v>30.35171840640883</v>
       </c>
       <c r="E72">
-        <v>29.33</v>
+        <v>29.749</v>
       </c>
       <c r="F72">
-        <v>29.33</v>
+        <v>29.749</v>
       </c>
       <c r="G72">
         <v>10.8</v>
@@ -7191,45 +7191,45 @@
         <v>5.71</v>
       </c>
       <c r="M72">
-        <v>1.880053</v>
+        <v>2.1389531</v>
       </c>
       <c r="N72">
-        <v>3.829947</v>
+        <v>3.5710469</v>
       </c>
       <c r="O72">
-        <v>0.7659894</v>
+        <v>0.71420938</v>
       </c>
       <c r="P72">
-        <v>3.0639576</v>
+        <v>2.85683752</v>
       </c>
       <c r="Q72">
-        <v>4.013957599999999</v>
+        <v>3.80683752</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1608338247843231</v>
+        <v>0.1645237630292092</v>
       </c>
       <c r="T72">
-        <v>1.939635545942126</v>
+        <v>2.001853205795923</v>
       </c>
       <c r="U72">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V72">
         <v>0.2</v>
       </c>
       <c r="W72">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>3.037148420815796</v>
+        <v>2.669530248232184</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08855109127847065</v>
+        <v>0.08858803512164438</v>
       </c>
       <c r="C73">
-        <v>11.40271840640883</v>
+        <v>10.97343629133255</v>
       </c>
       <c r="D73">
-        <v>30.35171840640883</v>
+        <v>30.34143629133256</v>
       </c>
       <c r="E73">
-        <v>29.749</v>
+        <v>30.168</v>
       </c>
       <c r="F73">
-        <v>29.749</v>
+        <v>30.168</v>
       </c>
       <c r="G73">
         <v>10.8</v>
@@ -7273,28 +7273,28 @@
         <v>5.71</v>
       </c>
       <c r="M73">
-        <v>2.1389531</v>
+        <v>2.1690792</v>
       </c>
       <c r="N73">
-        <v>3.5710469</v>
+        <v>3.5409208</v>
       </c>
       <c r="O73">
-        <v>0.71420938</v>
+        <v>0.7081841600000001</v>
       </c>
       <c r="P73">
-        <v>2.85683752</v>
+        <v>2.83273664</v>
       </c>
       <c r="Q73">
-        <v>3.80683752</v>
+        <v>3.78273664</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1645237630292091</v>
+        <v>0.168477268291587</v>
       </c>
       <c r="T73">
-        <v>2.001853205795922</v>
+        <v>2.068514984210705</v>
       </c>
       <c r="U73">
         <v>0.07190000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.669530248232184</v>
+        <v>2.632453439228959</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08858803512164438</v>
+        <v>0.08862497896481809</v>
       </c>
       <c r="C74">
-        <v>10.97343629133255</v>
+        <v>10.54416114034881</v>
       </c>
       <c r="D74">
-        <v>30.34143629133256</v>
+        <v>30.33116114034881</v>
       </c>
       <c r="E74">
-        <v>30.168</v>
+        <v>30.587</v>
       </c>
       <c r="F74">
-        <v>30.168</v>
+        <v>30.587</v>
       </c>
       <c r="G74">
         <v>10.8</v>
@@ -7355,28 +7355,28 @@
         <v>5.71</v>
       </c>
       <c r="M74">
-        <v>2.1690792</v>
+        <v>2.1992053</v>
       </c>
       <c r="N74">
-        <v>3.5409208</v>
+        <v>3.5107947</v>
       </c>
       <c r="O74">
-        <v>0.7081841600000001</v>
+        <v>0.70215894</v>
       </c>
       <c r="P74">
-        <v>2.83273664</v>
+        <v>2.80863576</v>
       </c>
       <c r="Q74">
-        <v>3.78273664</v>
+        <v>3.75863576</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.168477268291587</v>
+        <v>0.1727236257956226</v>
       </c>
       <c r="T74">
-        <v>2.068514984210705</v>
+        <v>2.140114672137693</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.632453439228959</v>
+        <v>2.596392433212125</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08862497896481809</v>
+        <v>0.08866192280799184</v>
       </c>
       <c r="C75">
-        <v>10.54416114034881</v>
+        <v>10.11489294638478</v>
       </c>
       <c r="D75">
-        <v>30.33116114034881</v>
+        <v>30.32089294638479</v>
       </c>
       <c r="E75">
-        <v>30.587</v>
+        <v>31.006</v>
       </c>
       <c r="F75">
-        <v>30.587</v>
+        <v>31.006</v>
       </c>
       <c r="G75">
         <v>10.8</v>
@@ -7437,28 +7437,28 @@
         <v>5.71</v>
       </c>
       <c r="M75">
-        <v>2.1992053</v>
+        <v>2.2293314</v>
       </c>
       <c r="N75">
-        <v>3.5107947</v>
+        <v>3.4806686</v>
       </c>
       <c r="O75">
-        <v>0.70215894</v>
+        <v>0.69613372</v>
       </c>
       <c r="P75">
-        <v>2.80863576</v>
+        <v>2.78453488</v>
       </c>
       <c r="Q75">
-        <v>3.75863576</v>
+        <v>3.73453488</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1727236257956226</v>
+        <v>0.1772966261845839</v>
       </c>
       <c r="T75">
-        <v>2.140114672137693</v>
+        <v>2.217222028366758</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.596392433212125</v>
+        <v>2.561306048979528</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08866192280799184</v>
+        <v>0.08869886665116557</v>
       </c>
       <c r="C76">
-        <v>10.11489294638478</v>
+        <v>9.685631702377293</v>
       </c>
       <c r="D76">
-        <v>30.32089294638479</v>
+        <v>30.31063170237729</v>
       </c>
       <c r="E76">
-        <v>31.006</v>
+        <v>31.425</v>
       </c>
       <c r="F76">
-        <v>31.006</v>
+        <v>31.425</v>
       </c>
       <c r="G76">
         <v>10.8</v>
@@ -7519,28 +7519,28 @@
         <v>5.71</v>
       </c>
       <c r="M76">
-        <v>2.2293314</v>
+        <v>2.2594575</v>
       </c>
       <c r="N76">
-        <v>3.4806686</v>
+        <v>3.4505425</v>
       </c>
       <c r="O76">
-        <v>0.69613372</v>
+        <v>0.6901085</v>
       </c>
       <c r="P76">
-        <v>2.78453488</v>
+        <v>2.760434</v>
       </c>
       <c r="Q76">
-        <v>3.73453488</v>
+        <v>3.710434</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1772966261845839</v>
+        <v>0.1822354666046622</v>
       </c>
       <c r="T76">
-        <v>2.217222028366758</v>
+        <v>2.300497973094149</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.561306048979528</v>
+        <v>2.527155301659801</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08869886665116557</v>
+        <v>0.09110701049433929</v>
       </c>
       <c r="C77">
-        <v>9.685631702377293</v>
+        <v>8.612421774788356</v>
       </c>
       <c r="D77">
-        <v>30.31063170237729</v>
+        <v>29.65642177478835</v>
       </c>
       <c r="E77">
-        <v>31.425</v>
+        <v>31.844</v>
       </c>
       <c r="F77">
-        <v>31.425</v>
+        <v>31.844</v>
       </c>
       <c r="G77">
         <v>10.8</v>
@@ -7601,45 +7601,45 @@
         <v>5.71</v>
       </c>
       <c r="M77">
-        <v>2.2594575</v>
+        <v>2.4137752</v>
       </c>
       <c r="N77">
-        <v>3.4505425</v>
+        <v>3.2962248</v>
       </c>
       <c r="O77">
-        <v>0.6901085</v>
+        <v>0.6592449600000001</v>
       </c>
       <c r="P77">
-        <v>2.760434</v>
+        <v>2.63697984</v>
       </c>
       <c r="Q77">
-        <v>3.710434</v>
+        <v>3.58697984</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1822354666046622</v>
+        <v>0.187585877059747</v>
       </c>
       <c r="T77">
-        <v>2.300497973094149</v>
+        <v>2.390713579882155</v>
       </c>
       <c r="U77">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V77">
         <v>0.2</v>
       </c>
       <c r="W77">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.527155301659801</v>
+        <v>2.365588974482794</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09110701049433929</v>
+        <v>0.09117515433751303</v>
       </c>
       <c r="C78">
-        <v>8.612421774788356</v>
+        <v>8.175320051375756</v>
       </c>
       <c r="D78">
-        <v>29.65642177478835</v>
+        <v>29.63832005137575</v>
       </c>
       <c r="E78">
-        <v>31.844</v>
+        <v>32.263</v>
       </c>
       <c r="F78">
-        <v>31.844</v>
+        <v>32.263</v>
       </c>
       <c r="G78">
         <v>10.8</v>
@@ -7683,28 +7683,28 @@
         <v>5.71</v>
       </c>
       <c r="M78">
-        <v>2.4137752</v>
+        <v>2.4455354</v>
       </c>
       <c r="N78">
-        <v>3.2962248</v>
+        <v>3.2644646</v>
       </c>
       <c r="O78">
-        <v>0.6592449600000001</v>
+        <v>0.65289292</v>
       </c>
       <c r="P78">
-        <v>2.63697984</v>
+        <v>2.61157168</v>
       </c>
       <c r="Q78">
-        <v>3.58697984</v>
+        <v>3.56157168</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.187585877059747</v>
+        <v>0.1934015405978827</v>
       </c>
       <c r="T78">
-        <v>2.390713579882155</v>
+        <v>2.48877402204303</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.365588974482794</v>
+        <v>2.334867039749251</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09117515433751303</v>
+        <v>0.09124329818068674</v>
       </c>
       <c r="C79">
-        <v>8.175320051375756</v>
+        <v>7.738240412387896</v>
       </c>
       <c r="D79">
-        <v>29.63832005137575</v>
+        <v>29.6202404123879</v>
       </c>
       <c r="E79">
-        <v>32.263</v>
+        <v>32.682</v>
       </c>
       <c r="F79">
-        <v>32.263</v>
+        <v>32.682</v>
       </c>
       <c r="G79">
         <v>10.8</v>
@@ -7765,28 +7765,28 @@
         <v>5.71</v>
       </c>
       <c r="M79">
-        <v>2.4455354</v>
+        <v>2.4772956</v>
       </c>
       <c r="N79">
-        <v>3.2644646</v>
+        <v>3.2327044</v>
       </c>
       <c r="O79">
-        <v>0.65289292</v>
+        <v>0.64654088</v>
       </c>
       <c r="P79">
-        <v>2.61157168</v>
+        <v>2.58616352</v>
       </c>
       <c r="Q79">
-        <v>3.56157168</v>
+        <v>3.53616352</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1934015405978827</v>
+        <v>0.1997459008213034</v>
       </c>
       <c r="T79">
-        <v>2.48877402204303</v>
+        <v>2.595749049854895</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.334867039749251</v>
+        <v>2.304932846931953</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09124329818068674</v>
+        <v>0.09131144202386048</v>
       </c>
       <c r="C80">
-        <v>7.738240412387896</v>
+        <v>7.301182817434338</v>
       </c>
       <c r="D80">
-        <v>29.6202404123879</v>
+        <v>29.60218281743434</v>
       </c>
       <c r="E80">
-        <v>32.682</v>
+        <v>33.101</v>
       </c>
       <c r="F80">
-        <v>32.682</v>
+        <v>33.101</v>
       </c>
       <c r="G80">
         <v>10.8</v>
@@ -7847,28 +7847,28 @@
         <v>5.71</v>
       </c>
       <c r="M80">
-        <v>2.4772956</v>
+        <v>2.5090558</v>
       </c>
       <c r="N80">
-        <v>3.2327044</v>
+        <v>3.2009442</v>
       </c>
       <c r="O80">
-        <v>0.64654088</v>
+        <v>0.64018884</v>
       </c>
       <c r="P80">
-        <v>2.58616352</v>
+        <v>2.56075536</v>
       </c>
       <c r="Q80">
-        <v>3.53616352</v>
+        <v>3.51075536</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1997459008213034</v>
+        <v>0.206694485827907</v>
       </c>
       <c r="T80">
-        <v>2.595749049854895</v>
+        <v>2.712912175553604</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.304932846931953</v>
+        <v>2.275756481780915</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09131144202386048</v>
+        <v>0.09137958586703421</v>
       </c>
       <c r="C81">
-        <v>7.301182817434338</v>
+        <v>6.864147226223061</v>
       </c>
       <c r="D81">
-        <v>29.60218281743434</v>
+        <v>29.58414722622306</v>
       </c>
       <c r="E81">
-        <v>33.101</v>
+        <v>33.52</v>
       </c>
       <c r="F81">
-        <v>33.101</v>
+        <v>33.52</v>
       </c>
       <c r="G81">
         <v>10.8</v>
@@ -7929,28 +7929,28 @@
         <v>5.71</v>
       </c>
       <c r="M81">
-        <v>2.5090558</v>
+        <v>2.540816</v>
       </c>
       <c r="N81">
-        <v>3.2009442</v>
+        <v>3.169184</v>
       </c>
       <c r="O81">
-        <v>0.64018884</v>
+        <v>0.6338368</v>
       </c>
       <c r="P81">
-        <v>2.56075536</v>
+        <v>2.535347199999999</v>
       </c>
       <c r="Q81">
-        <v>3.51075536</v>
+        <v>3.4853472</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.206694485827907</v>
+        <v>0.214337929335171</v>
       </c>
       <c r="T81">
-        <v>2.712912175553604</v>
+        <v>2.841791613822184</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.275756481780915</v>
+        <v>2.247309525758654</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09137958586703421</v>
+        <v>0.09144772971020793</v>
       </c>
       <c r="C82">
-        <v>6.864147226223061</v>
+        <v>6.427133598560182</v>
       </c>
       <c r="D82">
-        <v>29.58414722622306</v>
+        <v>29.56613359856019</v>
       </c>
       <c r="E82">
-        <v>33.52</v>
+        <v>33.939</v>
       </c>
       <c r="F82">
-        <v>33.52</v>
+        <v>33.939</v>
       </c>
       <c r="G82">
         <v>10.8</v>
@@ -8011,28 +8011,28 @@
         <v>5.71</v>
       </c>
       <c r="M82">
-        <v>2.540816</v>
+        <v>2.5725762</v>
       </c>
       <c r="N82">
-        <v>3.169184</v>
+        <v>3.1374238</v>
       </c>
       <c r="O82">
-        <v>0.6338368</v>
+        <v>0.62748476</v>
       </c>
       <c r="P82">
-        <v>2.535347199999999</v>
+        <v>2.50993904</v>
       </c>
       <c r="Q82">
-        <v>3.4853472</v>
+        <v>3.45993904</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.214337929335171</v>
+        <v>0.2227859458431997</v>
       </c>
       <c r="T82">
-        <v>2.841791613822184</v>
+        <v>2.984237308750615</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.247309525758654</v>
+        <v>2.219564963712251</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09144772971020793</v>
+        <v>0.09151587355338164</v>
       </c>
       <c r="C83">
-        <v>6.427133598560182</v>
+        <v>5.990141894349662</v>
       </c>
       <c r="D83">
-        <v>29.56613359856019</v>
+        <v>29.54814189434967</v>
       </c>
       <c r="E83">
-        <v>33.939</v>
+        <v>34.358</v>
       </c>
       <c r="F83">
-        <v>33.939</v>
+        <v>34.358</v>
       </c>
       <c r="G83">
         <v>10.8</v>
@@ -8093,28 +8093,28 @@
         <v>5.71</v>
       </c>
       <c r="M83">
-        <v>2.5725762</v>
+        <v>2.604336400000001</v>
       </c>
       <c r="N83">
-        <v>3.1374238</v>
+        <v>3.105663599999999</v>
       </c>
       <c r="O83">
-        <v>0.62748476</v>
+        <v>0.6211327199999999</v>
       </c>
       <c r="P83">
-        <v>2.50993904</v>
+        <v>2.484530879999999</v>
       </c>
       <c r="Q83">
-        <v>3.45993904</v>
+        <v>3.43453088</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2227859458431997</v>
+        <v>0.2321726308521203</v>
       </c>
       <c r="T83">
-        <v>2.984237308750615</v>
+        <v>3.142510303115537</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.219564963712251</v>
+        <v>2.192497098301125</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09151587355338164</v>
+        <v>0.09158401739655539</v>
       </c>
       <c r="C84">
-        <v>5.990141894349662</v>
+        <v>5.553172073592997</v>
       </c>
       <c r="D84">
-        <v>29.54814189434967</v>
+        <v>29.530172073593</v>
       </c>
       <c r="E84">
-        <v>34.358</v>
+        <v>34.777</v>
       </c>
       <c r="F84">
-        <v>34.358</v>
+        <v>34.777</v>
       </c>
       <c r="G84">
         <v>10.8</v>
@@ -8175,28 +8175,28 @@
         <v>5.71</v>
       </c>
       <c r="M84">
-        <v>2.604336400000001</v>
+        <v>2.6360966</v>
       </c>
       <c r="N84">
-        <v>3.105663599999999</v>
+        <v>3.0739034</v>
       </c>
       <c r="O84">
-        <v>0.6211327199999999</v>
+        <v>0.61478068</v>
       </c>
       <c r="P84">
-        <v>2.484530879999999</v>
+        <v>2.45912272</v>
       </c>
       <c r="Q84">
-        <v>3.43453088</v>
+        <v>3.40912272</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2321726308521203</v>
+        <v>0.2426636317444435</v>
       </c>
       <c r="T84">
-        <v>3.142510303115537</v>
+        <v>3.319403649758686</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.192497098301125</v>
+        <v>2.166081470610751</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09158401739655539</v>
+        <v>0.09165216123972911</v>
       </c>
       <c r="C85">
-        <v>5.553172073592997</v>
+        <v>5.116224096388912</v>
       </c>
       <c r="D85">
-        <v>29.530172073593</v>
+        <v>29.51222409638892</v>
       </c>
       <c r="E85">
-        <v>34.777</v>
+        <v>35.19600000000001</v>
       </c>
       <c r="F85">
-        <v>34.777</v>
+        <v>35.19600000000001</v>
       </c>
       <c r="G85">
         <v>10.8</v>
@@ -8257,28 +8257,28 @@
         <v>5.71</v>
       </c>
       <c r="M85">
-        <v>2.6360966</v>
+        <v>2.6678568</v>
       </c>
       <c r="N85">
-        <v>3.0739034</v>
+        <v>3.042143199999999</v>
       </c>
       <c r="O85">
-        <v>0.61478068</v>
+        <v>0.60842864</v>
       </c>
       <c r="P85">
-        <v>2.45912272</v>
+        <v>2.433714559999999</v>
       </c>
       <c r="Q85">
-        <v>3.40912272</v>
+        <v>3.38371456</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2426636317444435</v>
+        <v>0.254466007748307</v>
       </c>
       <c r="T85">
-        <v>3.319403649758686</v>
+        <v>3.518408664732229</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.166081470610751</v>
+        <v>2.140294786436813</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09165216123972911</v>
+        <v>0.09172030508290284</v>
       </c>
       <c r="C86">
-        <v>5.116224096388919</v>
+        <v>4.679297922933117</v>
       </c>
       <c r="D86">
-        <v>29.51222409638892</v>
+        <v>29.49429792293311</v>
       </c>
       <c r="E86">
-        <v>35.196</v>
+        <v>35.61499999999999</v>
       </c>
       <c r="F86">
-        <v>35.196</v>
+        <v>35.61499999999999</v>
       </c>
       <c r="G86">
         <v>10.8</v>
@@ -8339,28 +8339,28 @@
         <v>5.71</v>
       </c>
       <c r="M86">
-        <v>2.6678568</v>
+        <v>2.699617</v>
       </c>
       <c r="N86">
-        <v>3.0421432</v>
+        <v>3.010383</v>
       </c>
       <c r="O86">
-        <v>0.6084286400000001</v>
+        <v>0.6020766000000001</v>
       </c>
       <c r="P86">
-        <v>2.43371456</v>
+        <v>2.4083064</v>
       </c>
       <c r="Q86">
-        <v>3.38371456</v>
+        <v>3.3583064</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2544660077483069</v>
+        <v>0.2678420338860188</v>
       </c>
       <c r="T86">
-        <v>3.518408664732227</v>
+        <v>3.743947681702241</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.140294786436813</v>
+        <v>2.115114847772851</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09172030508290284</v>
+        <v>0.09178844892607657</v>
       </c>
       <c r="C87">
-        <v>4.679297922933117</v>
+        <v>4.242393513517904</v>
       </c>
       <c r="D87">
-        <v>29.49429792293311</v>
+        <v>29.4763935135179</v>
       </c>
       <c r="E87">
-        <v>35.61499999999999</v>
+        <v>36.034</v>
       </c>
       <c r="F87">
-        <v>35.61499999999999</v>
+        <v>36.034</v>
       </c>
       <c r="G87">
         <v>10.8</v>
@@ -8421,28 +8421,28 @@
         <v>5.71</v>
       </c>
       <c r="M87">
-        <v>2.699617</v>
+        <v>2.7313772</v>
       </c>
       <c r="N87">
-        <v>3.010383</v>
+        <v>2.9786228</v>
       </c>
       <c r="O87">
-        <v>0.6020766000000001</v>
+        <v>0.59572456</v>
       </c>
       <c r="P87">
-        <v>2.4083064</v>
+        <v>2.38289824</v>
       </c>
       <c r="Q87">
-        <v>3.3583064</v>
+        <v>3.33289824</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2678420338860188</v>
+        <v>0.2831289209005469</v>
       </c>
       <c r="T87">
-        <v>3.743947681702241</v>
+        <v>4.001706558239401</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.115114847772851</v>
+        <v>2.090520489077817</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09178844892607657</v>
+        <v>0.09185659276925029</v>
       </c>
       <c r="C88">
-        <v>4.242393513517904</v>
+        <v>3.805510828532</v>
       </c>
       <c r="D88">
-        <v>29.4763935135179</v>
+        <v>29.458510828532</v>
       </c>
       <c r="E88">
-        <v>36.034</v>
+        <v>36.453</v>
       </c>
       <c r="F88">
-        <v>36.034</v>
+        <v>36.453</v>
       </c>
       <c r="G88">
         <v>10.8</v>
@@ -8503,28 +8503,28 @@
         <v>5.71</v>
       </c>
       <c r="M88">
-        <v>2.7313772</v>
+        <v>2.7631374</v>
       </c>
       <c r="N88">
-        <v>2.9786228</v>
+        <v>2.9468626</v>
       </c>
       <c r="O88">
-        <v>0.59572456</v>
+        <v>0.5893725200000001</v>
       </c>
       <c r="P88">
-        <v>2.38289824</v>
+        <v>2.35749008</v>
       </c>
       <c r="Q88">
-        <v>3.33289824</v>
+        <v>3.30749008</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2831289209005469</v>
+        <v>0.3007676366865407</v>
       </c>
       <c r="T88">
-        <v>4.001706558239401</v>
+        <v>4.299120646551508</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.090520489077817</v>
+        <v>2.066491517938992</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09185659276925029</v>
+        <v>0.09192473661242404</v>
       </c>
       <c r="C89">
-        <v>3.805510828532</v>
+        <v>3.36864982846015</v>
       </c>
       <c r="D89">
-        <v>29.458510828532</v>
+        <v>29.44064982846015</v>
       </c>
       <c r="E89">
-        <v>36.453</v>
+        <v>36.872</v>
       </c>
       <c r="F89">
-        <v>36.453</v>
+        <v>36.872</v>
       </c>
       <c r="G89">
         <v>10.8</v>
@@ -8585,28 +8585,28 @@
         <v>5.71</v>
       </c>
       <c r="M89">
-        <v>2.7631374</v>
+        <v>2.7948976</v>
       </c>
       <c r="N89">
-        <v>2.9468626</v>
+        <v>2.9151024</v>
       </c>
       <c r="O89">
-        <v>0.5893725200000001</v>
+        <v>0.58302048</v>
       </c>
       <c r="P89">
-        <v>2.35749008</v>
+        <v>2.33208192</v>
       </c>
       <c r="Q89">
-        <v>3.30749008</v>
+        <v>3.28208192</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3007676366865407</v>
+        <v>0.3213461384368669</v>
       </c>
       <c r="T89">
-        <v>4.299120646551508</v>
+        <v>4.6461037495823</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.066491517938992</v>
+        <v>2.043008659780594</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09192473661242404</v>
+        <v>0.09199288045559775</v>
       </c>
       <c r="C90">
-        <v>3.36864982846015</v>
+        <v>2.931810473882898</v>
       </c>
       <c r="D90">
-        <v>29.44064982846015</v>
+        <v>29.42281047388289</v>
       </c>
       <c r="E90">
-        <v>36.872</v>
+        <v>37.291</v>
       </c>
       <c r="F90">
-        <v>36.872</v>
+        <v>37.291</v>
       </c>
       <c r="G90">
         <v>10.8</v>
@@ -8667,28 +8667,28 @@
         <v>5.71</v>
       </c>
       <c r="M90">
-        <v>2.7948976</v>
+        <v>2.8266578</v>
       </c>
       <c r="N90">
-        <v>2.9151024</v>
+        <v>2.8833422</v>
       </c>
       <c r="O90">
-        <v>0.58302048</v>
+        <v>0.5766684400000001</v>
       </c>
       <c r="P90">
-        <v>2.33208192</v>
+        <v>2.30667376</v>
       </c>
       <c r="Q90">
-        <v>3.28208192</v>
+        <v>3.25667376</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3213461384368669</v>
+        <v>0.3456661859599796</v>
       </c>
       <c r="T90">
-        <v>4.6461037495823</v>
+        <v>5.056174689527781</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.043008659780594</v>
+        <v>2.020053506299914</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09199288045559775</v>
+        <v>0.1022850242987715</v>
       </c>
       <c r="C91">
-        <v>2.931810473882898</v>
+        <v>0.04584058159714033</v>
       </c>
       <c r="D91">
-        <v>29.42281047388289</v>
+        <v>26.95584058159714</v>
       </c>
       <c r="E91">
-        <v>37.291</v>
+        <v>37.71</v>
       </c>
       <c r="F91">
-        <v>37.291</v>
+        <v>37.71</v>
       </c>
       <c r="G91">
         <v>10.8</v>
@@ -8749,45 +8749,45 @@
         <v>5.71</v>
       </c>
       <c r="M91">
-        <v>2.8266578</v>
+        <v>3.3939</v>
       </c>
       <c r="N91">
-        <v>2.8833422</v>
+        <v>2.3161</v>
       </c>
       <c r="O91">
-        <v>0.5766684400000001</v>
+        <v>0.46322</v>
       </c>
       <c r="P91">
-        <v>2.30667376</v>
+        <v>1.85288</v>
       </c>
       <c r="Q91">
-        <v>3.25667376</v>
+        <v>2.80288</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3456661859599796</v>
+        <v>0.3748502429877149</v>
       </c>
       <c r="T91">
-        <v>5.056174689527781</v>
+        <v>5.54825981746236</v>
       </c>
       <c r="U91">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V91">
         <v>0.2</v>
       </c>
       <c r="W91">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y91">
-        <v>2.020053506299914</v>
+        <v>1.682430242493886</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1022850242987715</v>
+        <v>0.1024667681419452</v>
       </c>
       <c r="C92">
-        <v>0.04584058159714033</v>
+        <v>-0.4130108474675538</v>
       </c>
       <c r="D92">
-        <v>26.95584058159714</v>
+        <v>26.91598915253245</v>
       </c>
       <c r="E92">
-        <v>37.71</v>
+        <v>38.129</v>
       </c>
       <c r="F92">
-        <v>37.71</v>
+        <v>38.129</v>
       </c>
       <c r="G92">
         <v>10.8</v>
@@ -8831,28 +8831,28 @@
         <v>5.71</v>
       </c>
       <c r="M92">
-        <v>3.3939</v>
+        <v>3.43161</v>
       </c>
       <c r="N92">
-        <v>2.3161</v>
+        <v>2.27839</v>
       </c>
       <c r="O92">
-        <v>0.46322</v>
+        <v>0.4556780000000001</v>
       </c>
       <c r="P92">
-        <v>1.85288</v>
+        <v>1.822712</v>
       </c>
       <c r="Q92">
-        <v>2.80288</v>
+        <v>2.772712</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3748502429877149</v>
+        <v>0.4105196460216135</v>
       </c>
       <c r="T92">
-        <v>5.54825981746236</v>
+        <v>6.149697196049066</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.682430242493886</v>
+        <v>1.663941998070877</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1024667681419452</v>
+        <v>0.1026485119851189</v>
       </c>
       <c r="C93">
-        <v>-0.4130108474675538</v>
+        <v>-0.871744618026014</v>
       </c>
       <c r="D93">
-        <v>26.91598915253245</v>
+        <v>26.87625538197399</v>
       </c>
       <c r="E93">
-        <v>38.129</v>
+        <v>38.548</v>
       </c>
       <c r="F93">
-        <v>38.129</v>
+        <v>38.548</v>
       </c>
       <c r="G93">
         <v>10.8</v>
@@ -8913,28 +8913,28 @@
         <v>5.71</v>
       </c>
       <c r="M93">
-        <v>3.43161</v>
+        <v>3.46932</v>
       </c>
       <c r="N93">
-        <v>2.27839</v>
+        <v>2.24068</v>
       </c>
       <c r="O93">
-        <v>0.4556780000000001</v>
+        <v>0.448136</v>
       </c>
       <c r="P93">
-        <v>1.822712</v>
+        <v>1.792544</v>
       </c>
       <c r="Q93">
-        <v>2.772712</v>
+        <v>2.742544</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4105196460216135</v>
+        <v>0.4551063998139869</v>
       </c>
       <c r="T93">
-        <v>6.149697196049066</v>
+        <v>6.90149391928245</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.663941998070877</v>
+        <v>1.645855672004888</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1026485119851189</v>
+        <v>0.1028302558282926</v>
       </c>
       <c r="C94">
-        <v>-0.871744618026014</v>
+        <v>-1.330361250377692</v>
       </c>
       <c r="D94">
-        <v>26.87625538197399</v>
+        <v>26.83663874962231</v>
       </c>
       <c r="E94">
-        <v>38.548</v>
+        <v>38.967</v>
       </c>
       <c r="F94">
-        <v>38.548</v>
+        <v>38.967</v>
       </c>
       <c r="G94">
         <v>10.8</v>
@@ -8995,28 +8995,28 @@
         <v>5.71</v>
       </c>
       <c r="M94">
-        <v>3.46932</v>
+        <v>3.50703</v>
       </c>
       <c r="N94">
-        <v>2.24068</v>
+        <v>2.20297</v>
       </c>
       <c r="O94">
-        <v>0.448136</v>
+        <v>0.440594</v>
       </c>
       <c r="P94">
-        <v>1.792544</v>
+        <v>1.762376</v>
       </c>
       <c r="Q94">
-        <v>2.742544</v>
+        <v>2.712376</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4551063998139869</v>
+        <v>0.5124322261184668</v>
       </c>
       <c r="T94">
-        <v>6.90149391928245</v>
+        <v>7.868089706296799</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.645855672004888</v>
+        <v>1.628158299187632</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1028302558282926</v>
+        <v>0.1030119996714664</v>
       </c>
       <c r="C95">
-        <v>-1.330361250377692</v>
+        <v>-1.788861261758811</v>
       </c>
       <c r="D95">
-        <v>26.83663874962231</v>
+        <v>26.79713873824119</v>
       </c>
       <c r="E95">
-        <v>38.967</v>
+        <v>39.386</v>
       </c>
       <c r="F95">
-        <v>38.967</v>
+        <v>39.386</v>
       </c>
       <c r="G95">
         <v>10.8</v>
@@ -9077,28 +9077,28 @@
         <v>5.71</v>
       </c>
       <c r="M95">
-        <v>3.50703</v>
+        <v>3.54474</v>
       </c>
       <c r="N95">
-        <v>2.20297</v>
+        <v>2.16526</v>
       </c>
       <c r="O95">
-        <v>0.440594</v>
+        <v>0.433052</v>
       </c>
       <c r="P95">
-        <v>1.762376</v>
+        <v>1.732208</v>
       </c>
       <c r="Q95">
-        <v>2.712376</v>
+        <v>2.682208</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5124322261184668</v>
+        <v>0.5888666611911069</v>
       </c>
       <c r="T95">
-        <v>7.868089706296799</v>
+        <v>9.156884088982599</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.628158299187632</v>
+        <v>1.61083746621755</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1030119996714664</v>
+        <v>0.1031937435146401</v>
       </c>
       <c r="C96">
-        <v>-1.788861261758811</v>
+        <v>-2.247245166364849</v>
       </c>
       <c r="D96">
-        <v>26.79713873824119</v>
+        <v>26.75775483363515</v>
       </c>
       <c r="E96">
-        <v>39.386</v>
+        <v>39.805</v>
       </c>
       <c r="F96">
-        <v>39.386</v>
+        <v>39.805</v>
       </c>
       <c r="G96">
         <v>10.8</v>
@@ -9159,28 +9159,28 @@
         <v>5.71</v>
       </c>
       <c r="M96">
-        <v>3.54474</v>
+        <v>3.58245</v>
       </c>
       <c r="N96">
-        <v>2.16526</v>
+        <v>2.12755</v>
       </c>
       <c r="O96">
-        <v>0.433052</v>
+        <v>0.4255100000000001</v>
       </c>
       <c r="P96">
-        <v>1.732208</v>
+        <v>1.70204</v>
       </c>
       <c r="Q96">
-        <v>2.682208</v>
+        <v>2.65204</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5888666611911069</v>
+        <v>0.6958748702928033</v>
       </c>
       <c r="T96">
-        <v>9.156884088982599</v>
+        <v>10.96119622474272</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.61083746621755</v>
+        <v>1.593881282362629</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1031937435146401</v>
+        <v>0.1033754873578139</v>
       </c>
       <c r="C97">
-        <v>-2.247245166364849</v>
+        <v>-2.705513475372861</v>
       </c>
       <c r="D97">
-        <v>26.75775483363515</v>
+        <v>26.71848652462714</v>
       </c>
       <c r="E97">
-        <v>39.805</v>
+        <v>40.224</v>
       </c>
       <c r="F97">
-        <v>39.805</v>
+        <v>40.224</v>
       </c>
       <c r="G97">
         <v>10.8</v>
@@ -9241,28 +9241,28 @@
         <v>5.71</v>
       </c>
       <c r="M97">
-        <v>3.58245</v>
+        <v>3.62016</v>
       </c>
       <c r="N97">
-        <v>2.12755</v>
+        <v>2.08984</v>
       </c>
       <c r="O97">
-        <v>0.4255100000000001</v>
+        <v>0.417968</v>
       </c>
       <c r="P97">
-        <v>1.70204</v>
+        <v>1.671872</v>
       </c>
       <c r="Q97">
-        <v>2.65204</v>
+        <v>2.621872</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6958748702928033</v>
+        <v>0.8563871839453476</v>
       </c>
       <c r="T97">
-        <v>10.96119622474272</v>
+        <v>13.66766442838291</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.593881282362629</v>
+        <v>1.577278352338018</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1033754873578138</v>
+        <v>0.1035572312009876</v>
       </c>
       <c r="C98">
-        <v>-2.705513475372847</v>
+        <v>-3.16366669696356</v>
       </c>
       <c r="D98">
-        <v>26.71848652462715</v>
+        <v>26.67933330303644</v>
       </c>
       <c r="E98">
-        <v>40.224</v>
+        <v>40.643</v>
       </c>
       <c r="F98">
-        <v>40.224</v>
+        <v>40.643</v>
       </c>
       <c r="G98">
         <v>10.8</v>
@@ -9323,28 +9323,28 @@
         <v>5.71</v>
       </c>
       <c r="M98">
-        <v>3.620159999999999</v>
+        <v>3.65787</v>
       </c>
       <c r="N98">
-        <v>2.089840000000001</v>
+        <v>2.05213</v>
       </c>
       <c r="O98">
-        <v>0.4179680000000001</v>
+        <v>0.410426</v>
       </c>
       <c r="P98">
-        <v>1.671872</v>
+        <v>1.641704</v>
       </c>
       <c r="Q98">
-        <v>2.621872000000001</v>
+        <v>2.591704</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8563871839453454</v>
+        <v>1.123907706699585</v>
       </c>
       <c r="T98">
-        <v>13.66766442838287</v>
+        <v>18.17844476778316</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.577278352338018</v>
+        <v>1.561017750767523</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1035572312009876</v>
+        <v>0.1037389750441613</v>
       </c>
       <c r="C99">
-        <v>-3.16366669696356</v>
+        <v>-3.621705336343325</v>
       </c>
       <c r="D99">
-        <v>26.67933330303644</v>
+        <v>26.64029466365668</v>
       </c>
       <c r="E99">
-        <v>40.643</v>
+        <v>41.062</v>
       </c>
       <c r="F99">
-        <v>40.643</v>
+        <v>41.062</v>
       </c>
       <c r="G99">
         <v>10.8</v>
@@ -9405,28 +9405,28 @@
         <v>5.71</v>
       </c>
       <c r="M99">
-        <v>3.65787</v>
+        <v>3.69558</v>
       </c>
       <c r="N99">
-        <v>2.05213</v>
+        <v>2.01442</v>
       </c>
       <c r="O99">
-        <v>0.410426</v>
+        <v>0.4028840000000001</v>
       </c>
       <c r="P99">
-        <v>1.641704</v>
+        <v>1.611536</v>
       </c>
       <c r="Q99">
-        <v>2.591704</v>
+        <v>2.561536</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.123907706699585</v>
+        <v>1.658948752208064</v>
       </c>
       <c r="T99">
-        <v>18.17844476778316</v>
+        <v>27.20000544658373</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.561017750767523</v>
+        <v>1.545088998208671</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1037389750441613</v>
+        <v>0.103920718887335</v>
       </c>
       <c r="C100">
-        <v>-3.621705336343325</v>
+        <v>-4.079629895765827</v>
       </c>
       <c r="D100">
-        <v>26.64029466365668</v>
+        <v>26.60137010423418</v>
       </c>
       <c r="E100">
-        <v>41.062</v>
+        <v>41.481</v>
       </c>
       <c r="F100">
-        <v>41.062</v>
+        <v>41.481</v>
       </c>
       <c r="G100">
         <v>10.8</v>
@@ -9487,28 +9487,28 @@
         <v>5.71</v>
       </c>
       <c r="M100">
-        <v>3.69558</v>
+        <v>3.73329</v>
       </c>
       <c r="N100">
-        <v>2.01442</v>
+        <v>1.97671</v>
       </c>
       <c r="O100">
-        <v>0.4028840000000001</v>
+        <v>0.395342</v>
       </c>
       <c r="P100">
-        <v>1.611536</v>
+        <v>1.581368</v>
       </c>
       <c r="Q100">
-        <v>2.561536</v>
+        <v>2.531368</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.658948752208064</v>
+        <v>3.2640718887335</v>
       </c>
       <c r="T100">
-        <v>27.20000544658373</v>
+        <v>54.26468748298545</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.545088998208671</v>
+        <v>1.529482038630805</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.103920718887335</v>
-      </c>
-      <c r="C101">
-        <v>-4.079629895765827</v>
-      </c>
-      <c r="D101">
-        <v>26.60137010423418</v>
-      </c>
-      <c r="E101">
-        <v>41.481</v>
-      </c>
-      <c r="F101">
-        <v>41.481</v>
-      </c>
-      <c r="G101">
-        <v>10.8</v>
-      </c>
-      <c r="H101">
-        <v>41.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>6.66</v>
-      </c>
-      <c r="K101">
-        <v>0.9500000000000002</v>
-      </c>
-      <c r="L101">
-        <v>5.71</v>
-      </c>
-      <c r="M101">
-        <v>3.73329</v>
-      </c>
-      <c r="N101">
-        <v>1.97671</v>
-      </c>
-      <c r="O101">
-        <v>0.395342</v>
-      </c>
-      <c r="P101">
-        <v>1.581368</v>
-      </c>
-      <c r="Q101">
-        <v>2.531368</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.2640718887335</v>
-      </c>
-      <c r="T101">
-        <v>54.26468748298545</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.529482038630805</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
